--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2785CCEF-BBF5-4201-A679-E7512476A6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650EFCDA-CBD8-4531-A845-12DDA50F8C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -109,29 +109,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -153,7 +153,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -170,7 +170,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -185,9 +185,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -209,14 +214,14 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -230,26 +235,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1651,6 +1657,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2988,6 +2997,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>2623</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>2551</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4360,6 +4372,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5697,6 +5712,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>1206</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7069,6 +7087,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8406,6 +8427,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>4442</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4412</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9778,6 +9802,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11115,6 +11142,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>1203</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12487,6 +12517,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13824,6 +13857,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>1225</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1349</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15198,6 +15234,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16535,6 +16574,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>5992</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>5634</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17923,6 +17965,9 @@
                 <c:pt idx="442">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="443">
+                  <c:v>46209</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19260,6 +19305,9 @@
                 </c:pt>
                 <c:pt idx="442">
                   <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20406,18 +20454,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K444"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K445"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="7.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="7.19921875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
@@ -20430,29 +20479,29 @@
       <c r="D1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>43100</v>
       </c>
@@ -20487,7 +20536,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>43107</v>
       </c>
@@ -20522,7 +20571,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>43114</v>
       </c>
@@ -20557,7 +20606,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>43121</v>
       </c>
@@ -20592,7 +20641,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>43128</v>
       </c>
@@ -20627,7 +20676,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>43135</v>
       </c>
@@ -20662,7 +20711,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>43142</v>
       </c>
@@ -20697,7 +20746,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>43149</v>
       </c>
@@ -20732,7 +20781,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>43156</v>
       </c>
@@ -20767,7 +20816,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>43163</v>
       </c>
@@ -20802,7 +20851,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>43170</v>
       </c>
@@ -20837,7 +20886,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>43177</v>
       </c>
@@ -20872,7 +20921,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>43184</v>
       </c>
@@ -20907,7 +20956,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>43191</v>
       </c>
@@ -20942,7 +20991,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>43198</v>
       </c>
@@ -20977,7 +21026,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>43205</v>
       </c>
@@ -21012,7 +21061,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>43212</v>
       </c>
@@ -21047,7 +21096,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>43219</v>
       </c>
@@ -21082,7 +21131,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>43226</v>
       </c>
@@ -21117,7 +21166,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>43233</v>
       </c>
@@ -21152,7 +21201,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>43240</v>
       </c>
@@ -21187,7 +21236,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>43247</v>
       </c>
@@ -21222,7 +21271,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>43254</v>
       </c>
@@ -21257,7 +21306,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>43261</v>
       </c>
@@ -21292,7 +21341,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>43268</v>
       </c>
@@ -21327,7 +21376,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>43275</v>
       </c>
@@ -21362,7 +21411,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>43282</v>
       </c>
@@ -21397,7 +21446,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>43289</v>
       </c>
@@ -21432,7 +21481,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>43296</v>
       </c>
@@ -21467,7 +21516,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>43303</v>
       </c>
@@ -21502,7 +21551,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>43310</v>
       </c>
@@ -21537,7 +21586,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>43317</v>
       </c>
@@ -21572,7 +21621,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>43324</v>
       </c>
@@ -21607,7 +21656,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>43331</v>
       </c>
@@ -21642,7 +21691,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>43338</v>
       </c>
@@ -21677,7 +21726,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>43345</v>
       </c>
@@ -21712,7 +21761,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>43352</v>
       </c>
@@ -21747,7 +21796,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>43359</v>
       </c>
@@ -21782,7 +21831,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>43366</v>
       </c>
@@ -21817,7 +21866,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>43373</v>
       </c>
@@ -21852,7 +21901,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>43380</v>
       </c>
@@ -21887,7 +21936,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>43387</v>
       </c>
@@ -21922,7 +21971,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>43394</v>
       </c>
@@ -21957,7 +22006,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>43401</v>
       </c>
@@ -21992,7 +22041,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>43408</v>
       </c>
@@ -22027,7 +22076,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>43415</v>
       </c>
@@ -22062,7 +22111,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>43422</v>
       </c>
@@ -22097,7 +22146,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>43429</v>
       </c>
@@ -22132,7 +22181,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>43436</v>
       </c>
@@ -22167,7 +22216,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>43443</v>
       </c>
@@ -22202,7 +22251,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>43450</v>
       </c>
@@ -22237,7 +22286,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>43457</v>
       </c>
@@ -22272,7 +22321,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43464</v>
       </c>
@@ -22307,7 +22356,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>43471</v>
       </c>
@@ -22342,7 +22391,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43478</v>
       </c>
@@ -22377,7 +22426,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>43485</v>
       </c>
@@ -22412,7 +22461,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43492</v>
       </c>
@@ -22447,7 +22496,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>43499</v>
       </c>
@@ -22482,7 +22531,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43506</v>
       </c>
@@ -22517,7 +22566,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>43513</v>
       </c>
@@ -22552,7 +22601,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43520</v>
       </c>
@@ -22587,7 +22636,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>43527</v>
       </c>
@@ -22622,7 +22671,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43534</v>
       </c>
@@ -22657,7 +22706,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>43541</v>
       </c>
@@ -22692,7 +22741,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43548</v>
       </c>
@@ -22727,7 +22776,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>43555</v>
       </c>
@@ -22762,7 +22811,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43562</v>
       </c>
@@ -22797,7 +22846,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>43569</v>
       </c>
@@ -22832,7 +22881,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43576</v>
       </c>
@@ -22867,7 +22916,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>43583</v>
       </c>
@@ -22902,7 +22951,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43590</v>
       </c>
@@ -22937,7 +22986,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>43597</v>
       </c>
@@ -22972,7 +23021,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43604</v>
       </c>
@@ -23007,7 +23056,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>43611</v>
       </c>
@@ -23042,7 +23091,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43618</v>
       </c>
@@ -23077,7 +23126,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>43625</v>
       </c>
@@ -23112,7 +23161,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43632</v>
       </c>
@@ -23147,7 +23196,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>43639</v>
       </c>
@@ -23182,7 +23231,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43646</v>
       </c>
@@ -23217,7 +23266,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="10">
         <v>43653</v>
       </c>
@@ -23252,7 +23301,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43660</v>
       </c>
@@ -23287,7 +23336,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="10">
         <v>43667</v>
       </c>
@@ -23322,7 +23371,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43674</v>
       </c>
@@ -23357,7 +23406,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>43681</v>
       </c>
@@ -23392,7 +23441,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>43688</v>
       </c>
@@ -23427,7 +23476,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>43695</v>
       </c>
@@ -23462,7 +23511,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>43702</v>
       </c>
@@ -23497,7 +23546,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="10">
         <v>43709</v>
       </c>
@@ -23532,7 +23581,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>43716</v>
       </c>
@@ -23567,7 +23616,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <v>43723</v>
       </c>
@@ -23602,7 +23651,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>43730</v>
       </c>
@@ -23637,7 +23686,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <v>43737</v>
       </c>
@@ -23672,7 +23721,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>43744</v>
       </c>
@@ -23707,7 +23756,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <v>43751</v>
       </c>
@@ -23742,7 +23791,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>43758</v>
       </c>
@@ -23777,7 +23826,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>43765</v>
       </c>
@@ -23812,7 +23861,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>43772</v>
       </c>
@@ -23847,7 +23896,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>43779</v>
       </c>
@@ -23882,7 +23931,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>43786</v>
       </c>
@@ -23917,7 +23966,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>43793</v>
       </c>
@@ -23952,7 +24001,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>43800</v>
       </c>
@@ -23987,7 +24036,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>43807</v>
       </c>
@@ -24022,7 +24071,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>43814</v>
       </c>
@@ -24057,7 +24106,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>43821</v>
       </c>
@@ -24092,7 +24141,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>43828</v>
       </c>
@@ -24127,7 +24176,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>43835</v>
       </c>
@@ -24162,7 +24211,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>43842</v>
       </c>
@@ -24197,7 +24246,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>43849</v>
       </c>
@@ -24232,7 +24281,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>43856</v>
       </c>
@@ -24267,7 +24316,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>43863</v>
       </c>
@@ -24302,7 +24351,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>43870</v>
       </c>
@@ -24337,7 +24386,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>43877</v>
       </c>
@@ -24372,7 +24421,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>43884</v>
       </c>
@@ -24407,7 +24456,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>43891</v>
       </c>
@@ -24442,7 +24491,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>43898</v>
       </c>
@@ -24477,7 +24526,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>43905</v>
       </c>
@@ -24512,7 +24561,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>43912</v>
       </c>
@@ -24547,7 +24596,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>43919</v>
       </c>
@@ -24582,7 +24631,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>43926</v>
       </c>
@@ -24617,7 +24666,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="10">
         <v>43933</v>
       </c>
@@ -24652,7 +24701,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>43940</v>
       </c>
@@ -24687,7 +24736,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="10">
         <v>43947</v>
       </c>
@@ -24722,7 +24771,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>43954</v>
       </c>
@@ -24757,7 +24806,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>43961</v>
       </c>
@@ -24792,7 +24841,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>43968</v>
       </c>
@@ -24827,7 +24876,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="10">
         <v>43975</v>
       </c>
@@ -24862,7 +24911,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>43982</v>
       </c>
@@ -24897,7 +24946,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>43989</v>
       </c>
@@ -24932,7 +24981,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>43996</v>
       </c>
@@ -24967,7 +25016,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>44003</v>
       </c>
@@ -25002,7 +25051,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>44010</v>
       </c>
@@ -25037,7 +25086,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>44017</v>
       </c>
@@ -25072,7 +25121,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>44024</v>
       </c>
@@ -25107,7 +25156,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44031</v>
       </c>
@@ -25142,7 +25191,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>44038</v>
       </c>
@@ -25177,7 +25226,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44045</v>
       </c>
@@ -25212,7 +25261,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>44052</v>
       </c>
@@ -25247,7 +25296,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44059</v>
       </c>
@@ -25282,7 +25331,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>44066</v>
       </c>
@@ -25317,7 +25366,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44073</v>
       </c>
@@ -25352,7 +25401,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>44080</v>
       </c>
@@ -25387,7 +25436,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>44087</v>
       </c>
@@ -25422,7 +25471,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>44094</v>
       </c>
@@ -25457,7 +25506,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>44101</v>
       </c>
@@ -25492,7 +25541,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>44108</v>
       </c>
@@ -25527,7 +25576,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>44115</v>
       </c>
@@ -25562,7 +25611,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>44122</v>
       </c>
@@ -25597,7 +25646,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44129</v>
       </c>
@@ -25632,7 +25681,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>44136</v>
       </c>
@@ -25667,7 +25716,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>44143</v>
       </c>
@@ -25702,7 +25751,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>44150</v>
       </c>
@@ -25737,7 +25786,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>44157</v>
       </c>
@@ -25772,7 +25821,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>44164</v>
       </c>
@@ -25807,7 +25856,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>44171</v>
       </c>
@@ -25842,7 +25891,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>44178</v>
       </c>
@@ -25877,7 +25926,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>44185</v>
       </c>
@@ -25912,7 +25961,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>44192</v>
       </c>
@@ -25947,7 +25996,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>44199</v>
       </c>
@@ -25982,7 +26031,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44206</v>
       </c>
@@ -26017,7 +26066,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>44213</v>
       </c>
@@ -26052,7 +26101,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44220</v>
       </c>
@@ -26087,7 +26136,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>44227</v>
       </c>
@@ -26122,7 +26171,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>44234</v>
       </c>
@@ -26157,7 +26206,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>44241</v>
       </c>
@@ -26192,7 +26241,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>44248</v>
       </c>
@@ -26227,7 +26276,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>44255</v>
       </c>
@@ -26262,7 +26311,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>44262</v>
       </c>
@@ -26297,7 +26346,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>44269</v>
       </c>
@@ -26332,7 +26381,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>44276</v>
       </c>
@@ -26367,7 +26416,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>44283</v>
       </c>
@@ -26402,7 +26451,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>44290</v>
       </c>
@@ -26437,7 +26486,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>44297</v>
       </c>
@@ -26472,7 +26521,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>44304</v>
       </c>
@@ -26507,7 +26556,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>44311</v>
       </c>
@@ -26542,7 +26591,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>44318</v>
       </c>
@@ -26577,7 +26626,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>44325</v>
       </c>
@@ -26612,7 +26661,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>44332</v>
       </c>
@@ -26647,7 +26696,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>44339</v>
       </c>
@@ -26682,7 +26731,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>44346</v>
       </c>
@@ -26717,7 +26766,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>44353</v>
       </c>
@@ -26752,7 +26801,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="10">
         <v>44360</v>
       </c>
@@ -26787,7 +26836,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>44367</v>
       </c>
@@ -26822,7 +26871,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>44374</v>
       </c>
@@ -26857,7 +26906,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>44381</v>
       </c>
@@ -26892,7 +26941,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>44388</v>
       </c>
@@ -26927,7 +26976,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>44395</v>
       </c>
@@ -26962,7 +27011,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>44402</v>
       </c>
@@ -26997,7 +27046,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>44409</v>
       </c>
@@ -27032,7 +27081,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>44416</v>
       </c>
@@ -27067,7 +27116,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="10">
         <v>44423</v>
       </c>
@@ -27102,7 +27151,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>44430</v>
       </c>
@@ -27137,7 +27186,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="10">
         <v>44437</v>
       </c>
@@ -27172,7 +27221,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>44444</v>
       </c>
@@ -27207,7 +27256,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="10">
         <v>44451</v>
       </c>
@@ -27242,7 +27291,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>44458</v>
       </c>
@@ -27277,7 +27326,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="10">
         <v>44465</v>
       </c>
@@ -27312,7 +27361,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>44472</v>
       </c>
@@ -27347,7 +27396,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="10">
         <v>44479</v>
       </c>
@@ -27382,7 +27431,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>44486</v>
       </c>
@@ -27417,7 +27466,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="10">
         <v>44493</v>
       </c>
@@ -27452,7 +27501,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>44500</v>
       </c>
@@ -27487,7 +27536,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <v>44507</v>
       </c>
@@ -27522,7 +27571,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>44514</v>
       </c>
@@ -27557,7 +27606,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <v>44521</v>
       </c>
@@ -27592,7 +27641,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>44528</v>
       </c>
@@ -27627,7 +27676,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <v>44535</v>
       </c>
@@ -27662,7 +27711,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>44542</v>
       </c>
@@ -27697,7 +27746,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>44549</v>
       </c>
@@ -27732,7 +27781,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="10">
         <v>44556</v>
       </c>
@@ -27767,7 +27816,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>44563</v>
       </c>
@@ -27802,7 +27851,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="10">
         <v>44570</v>
       </c>
@@ -27837,7 +27886,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>44577</v>
       </c>
@@ -27872,7 +27921,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="10">
         <v>44584</v>
       </c>
@@ -27907,7 +27956,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>44591</v>
       </c>
@@ -27942,7 +27991,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="10">
         <v>44598</v>
       </c>
@@ -27977,7 +28026,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>44605</v>
       </c>
@@ -28012,7 +28061,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="10">
         <v>44612</v>
       </c>
@@ -28047,7 +28096,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>44619</v>
       </c>
@@ -28082,7 +28131,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="10">
         <v>44626</v>
       </c>
@@ -28117,7 +28166,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>44633</v>
       </c>
@@ -28152,7 +28201,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>44640</v>
       </c>
@@ -28187,7 +28236,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>44647</v>
       </c>
@@ -28222,7 +28271,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>44654</v>
       </c>
@@ -28257,7 +28306,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>44661</v>
       </c>
@@ -28292,7 +28341,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>44668</v>
       </c>
@@ -28327,7 +28376,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>44675</v>
       </c>
@@ -28362,7 +28411,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>44682</v>
       </c>
@@ -28397,7 +28446,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="10">
         <v>44689</v>
       </c>
@@ -28432,7 +28481,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>44696</v>
       </c>
@@ -28467,7 +28516,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="10">
         <v>44703</v>
       </c>
@@ -28502,7 +28551,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>44710</v>
       </c>
@@ -28537,7 +28586,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" s="10">
         <v>44717</v>
       </c>
@@ -28572,7 +28621,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>44724</v>
       </c>
@@ -28607,7 +28656,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="10">
         <v>44731</v>
       </c>
@@ -28642,7 +28691,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>44738</v>
       </c>
@@ -28677,7 +28726,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="10">
         <v>44745</v>
       </c>
@@ -28712,7 +28761,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>44752</v>
       </c>
@@ -28747,7 +28796,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" s="10">
         <v>44759</v>
       </c>
@@ -28782,7 +28831,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>44766</v>
       </c>
@@ -28817,7 +28866,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="10">
         <v>44773</v>
       </c>
@@ -28852,7 +28901,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="10">
         <v>44780</v>
       </c>
@@ -28887,7 +28936,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="10">
         <v>44787</v>
       </c>
@@ -28922,7 +28971,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>44794</v>
       </c>
@@ -28957,7 +29006,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" s="10">
         <v>44801</v>
       </c>
@@ -28992,7 +29041,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="10">
         <v>44808</v>
       </c>
@@ -29027,7 +29076,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>44815</v>
       </c>
@@ -29062,7 +29111,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="10">
         <v>44822</v>
       </c>
@@ -29097,7 +29146,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>44829</v>
       </c>
@@ -29132,7 +29181,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="10">
         <v>44836</v>
       </c>
@@ -29167,7 +29216,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>44843</v>
       </c>
@@ -29202,7 +29251,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" s="10">
         <v>44850</v>
       </c>
@@ -29237,7 +29286,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>44857</v>
       </c>
@@ -29272,7 +29321,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="10">
         <v>44864</v>
       </c>
@@ -29307,7 +29356,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>44871</v>
       </c>
@@ -29342,7 +29391,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="10">
         <v>44878</v>
       </c>
@@ -29377,7 +29426,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>44885</v>
       </c>
@@ -29412,7 +29461,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" s="10">
         <v>44892</v>
       </c>
@@ -29447,7 +29496,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>44899</v>
       </c>
@@ -29482,7 +29531,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="10">
         <v>44906</v>
       </c>
@@ -29517,7 +29566,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="10">
         <v>44913</v>
       </c>
@@ -29552,7 +29601,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="10">
         <v>44920</v>
       </c>
@@ -29587,7 +29636,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="10">
         <v>44927</v>
       </c>
@@ -29622,7 +29671,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="10">
         <v>44934</v>
       </c>
@@ -29657,7 +29706,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" s="10">
         <v>44941</v>
       </c>
@@ -29692,7 +29741,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="10">
         <v>44948</v>
       </c>
@@ -29727,7 +29776,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="10">
         <v>44955</v>
       </c>
@@ -29762,7 +29811,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>44962</v>
       </c>
@@ -29797,7 +29846,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="10">
         <v>44969</v>
       </c>
@@ -29832,7 +29881,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="10">
         <v>44976</v>
       </c>
@@ -29867,7 +29916,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="10">
         <v>44983</v>
       </c>
@@ -29902,7 +29951,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="10">
         <v>44990</v>
       </c>
@@ -29937,7 +29986,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="10">
         <v>44997</v>
       </c>
@@ -29972,7 +30021,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="10">
         <v>45004</v>
       </c>
@@ -30007,7 +30056,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="10">
         <v>45011</v>
       </c>
@@ -30042,7 +30091,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="10">
         <v>45018</v>
       </c>
@@ -30077,7 +30126,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="10">
         <v>45025</v>
       </c>
@@ -30112,7 +30161,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="10">
         <v>45032</v>
       </c>
@@ -30147,7 +30196,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="10">
         <v>45039</v>
       </c>
@@ -30182,7 +30231,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="10">
         <v>45046</v>
       </c>
@@ -30217,7 +30266,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="10">
         <v>45053</v>
       </c>
@@ -30252,7 +30301,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="10">
         <v>45060</v>
       </c>
@@ -30287,7 +30336,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="10">
         <v>45067</v>
       </c>
@@ -30322,7 +30371,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="10">
         <v>45074</v>
       </c>
@@ -30357,7 +30406,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="10">
         <v>45081</v>
       </c>
@@ -30392,7 +30441,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="10">
         <v>45088</v>
       </c>
@@ -30427,7 +30476,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="10">
         <v>45095</v>
       </c>
@@ -30462,7 +30511,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="10">
         <v>45102</v>
       </c>
@@ -30497,7 +30546,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="10">
         <v>45109</v>
       </c>
@@ -30532,7 +30581,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="10">
         <v>45116</v>
       </c>
@@ -30567,7 +30616,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="10">
         <v>45123</v>
       </c>
@@ -30602,7 +30651,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="10">
         <v>45130</v>
       </c>
@@ -30637,7 +30686,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="10">
         <v>45137</v>
       </c>
@@ -30672,7 +30721,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="10">
         <v>45144</v>
       </c>
@@ -30707,7 +30756,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="10">
         <v>45151</v>
       </c>
@@ -30742,7 +30791,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="10">
         <v>45158</v>
       </c>
@@ -30777,7 +30826,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="10">
         <v>45165</v>
       </c>
@@ -30812,7 +30861,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="10">
         <v>45172</v>
       </c>
@@ -30847,7 +30896,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="10">
         <v>45179</v>
       </c>
@@ -30882,7 +30931,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="10">
         <v>45186</v>
       </c>
@@ -30917,7 +30966,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="10">
         <v>45193</v>
       </c>
@@ -30952,7 +31001,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="10">
         <v>45200</v>
       </c>
@@ -30987,7 +31036,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="10">
         <v>45207</v>
       </c>
@@ -31022,7 +31071,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="10">
         <v>45214</v>
       </c>
@@ -31057,7 +31106,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="10">
         <v>45221</v>
       </c>
@@ -31092,7 +31141,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="10">
         <v>45228</v>
       </c>
@@ -31127,7 +31176,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="10">
         <v>45235</v>
       </c>
@@ -31162,7 +31211,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="10">
         <v>45242</v>
       </c>
@@ -31197,7 +31246,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="10">
         <v>45249</v>
       </c>
@@ -31232,7 +31281,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="10">
         <v>45256</v>
       </c>
@@ -31267,7 +31316,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="10">
         <v>45263</v>
       </c>
@@ -31302,7 +31351,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="10">
         <v>45270</v>
       </c>
@@ -31337,7 +31386,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="10">
         <v>45277</v>
       </c>
@@ -31372,7 +31421,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="10">
         <v>45284</v>
       </c>
@@ -31407,7 +31456,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" s="10">
         <v>45291</v>
       </c>
@@ -31442,7 +31491,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="10">
         <v>45298</v>
       </c>
@@ -31477,7 +31526,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="10">
         <v>45305</v>
       </c>
@@ -31512,7 +31561,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="10">
         <v>45312</v>
       </c>
@@ -31547,7 +31596,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="10">
         <v>45319</v>
       </c>
@@ -31582,7 +31631,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" s="10">
         <v>45326</v>
       </c>
@@ -31617,7 +31666,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="10">
         <v>45333</v>
       </c>
@@ -31652,7 +31701,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="10">
         <v>45340</v>
       </c>
@@ -31687,7 +31736,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="10">
         <v>45347</v>
       </c>
@@ -31722,7 +31771,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="10">
         <v>45354</v>
       </c>
@@ -31757,7 +31806,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="10">
         <v>45361</v>
       </c>
@@ -31792,7 +31841,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="10">
         <v>45368</v>
       </c>
@@ -31827,7 +31876,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" s="10">
         <v>45375</v>
       </c>
@@ -31862,7 +31911,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="10">
         <v>45382</v>
       </c>
@@ -31897,7 +31946,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="10">
         <v>45389</v>
       </c>
@@ -31932,7 +31981,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="10">
         <v>45396</v>
       </c>
@@ -31967,7 +32016,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="10">
         <v>45403</v>
       </c>
@@ -32002,7 +32051,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="10">
         <v>45410</v>
       </c>
@@ -32037,7 +32086,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" s="10">
         <v>45417</v>
       </c>
@@ -32072,7 +32121,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" s="10">
         <v>45424</v>
       </c>
@@ -32107,7 +32156,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" s="10">
         <v>45431</v>
       </c>
@@ -32142,7 +32191,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" s="10">
         <v>45438</v>
       </c>
@@ -32177,7 +32226,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" s="10">
         <v>45445</v>
       </c>
@@ -32212,7 +32261,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="10">
         <v>45452</v>
       </c>
@@ -32247,7 +32296,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="10">
         <v>45459</v>
       </c>
@@ -32282,7 +32331,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="10">
         <v>45466</v>
       </c>
@@ -32317,7 +32366,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="10">
         <v>45473</v>
       </c>
@@ -32352,7 +32401,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="10">
         <v>45480</v>
       </c>
@@ -32387,7 +32436,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="10">
         <v>45487</v>
       </c>
@@ -32422,7 +32471,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="10">
         <v>45494</v>
       </c>
@@ -32457,7 +32506,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="10">
         <v>45501</v>
       </c>
@@ -32492,7 +32541,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="10">
         <v>45508</v>
       </c>
@@ -32527,7 +32576,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="10">
         <v>45515</v>
       </c>
@@ -32562,7 +32611,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="10">
         <v>45522</v>
       </c>
@@ -32597,7 +32646,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="10">
         <v>45529</v>
       </c>
@@ -32632,7 +32681,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="10">
         <v>45536</v>
       </c>
@@ -32667,7 +32716,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="10">
         <v>45543</v>
       </c>
@@ -32702,7 +32751,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="10">
         <v>45550</v>
       </c>
@@ -32737,7 +32786,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="10">
         <v>45557</v>
       </c>
@@ -32772,7 +32821,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="10">
         <v>45564</v>
       </c>
@@ -32807,7 +32856,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="10">
         <v>45571</v>
       </c>
@@ -32842,7 +32891,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="10">
         <v>45578</v>
       </c>
@@ -32877,7 +32926,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="10">
         <v>45585</v>
       </c>
@@ -32912,7 +32961,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="10">
         <v>45592</v>
       </c>
@@ -32947,7 +32996,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="10">
         <v>45599</v>
       </c>
@@ -32982,7 +33031,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="10">
         <v>45606</v>
       </c>
@@ -33017,7 +33066,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="10">
         <v>45613</v>
       </c>
@@ -33052,7 +33101,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="10">
         <v>45620</v>
       </c>
@@ -33087,7 +33136,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="10">
         <v>45627</v>
       </c>
@@ -33122,7 +33171,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="10">
         <v>45634</v>
       </c>
@@ -33157,7 +33206,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="10">
         <v>45641</v>
       </c>
@@ -33192,7 +33241,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" s="10">
         <v>45648</v>
       </c>
@@ -33227,7 +33276,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" s="10">
         <v>45655</v>
       </c>
@@ -33262,7 +33311,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" s="10">
         <v>45662</v>
       </c>
@@ -33297,7 +33346,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="10">
         <v>45669</v>
       </c>
@@ -33332,7 +33381,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="10">
         <v>45676</v>
       </c>
@@ -33367,7 +33416,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="10">
         <v>45683</v>
       </c>
@@ -33402,7 +33451,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="10">
         <v>45690</v>
       </c>
@@ -33437,7 +33486,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="10">
         <v>45697</v>
       </c>
@@ -33472,7 +33521,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="10">
         <v>45704</v>
       </c>
@@ -33507,7 +33556,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="10">
         <v>45711</v>
       </c>
@@ -33542,7 +33591,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="10">
         <v>45718</v>
       </c>
@@ -33577,7 +33626,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="10">
         <v>45725</v>
       </c>
@@ -33612,7 +33661,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="10">
         <v>45732</v>
       </c>
@@ -33647,7 +33696,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="10">
         <v>45739</v>
       </c>
@@ -33682,7 +33731,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="10">
         <v>45746</v>
       </c>
@@ -33717,7 +33766,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="10">
         <v>45753</v>
       </c>
@@ -33752,7 +33801,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="10">
         <v>45760</v>
       </c>
@@ -33787,7 +33836,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="10">
         <v>45767</v>
       </c>
@@ -33822,7 +33871,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="10">
         <v>45774</v>
       </c>
@@ -33857,7 +33906,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" s="10">
         <v>45781</v>
       </c>
@@ -33892,7 +33941,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" s="10">
         <v>45788</v>
       </c>
@@ -33927,7 +33976,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" s="10">
         <v>45795</v>
       </c>
@@ -33962,7 +34011,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="10">
         <v>45802</v>
       </c>
@@ -33997,7 +34046,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" s="10">
         <v>45809</v>
       </c>
@@ -34032,7 +34081,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" s="10">
         <v>45816</v>
       </c>
@@ -34067,7 +34116,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="10">
         <v>45823</v>
       </c>
@@ -34102,7 +34151,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="10">
         <v>45830</v>
       </c>
@@ -34137,7 +34186,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="10">
         <v>45837</v>
       </c>
@@ -34172,7 +34221,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="10">
         <v>45844</v>
       </c>
@@ -34207,7 +34256,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="10">
         <v>45851</v>
       </c>
@@ -34242,7 +34291,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="10">
         <v>45858</v>
       </c>
@@ -34277,7 +34326,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="10">
         <v>45865</v>
       </c>
@@ -34312,7 +34361,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="10">
         <v>45872</v>
       </c>
@@ -34347,7 +34396,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="10">
         <v>45879</v>
       </c>
@@ -34382,7 +34431,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="10">
         <v>45886</v>
       </c>
@@ -34417,7 +34466,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="10">
         <v>45893</v>
       </c>
@@ -34452,7 +34501,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="10">
         <v>45900</v>
       </c>
@@ -34487,7 +34536,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="10">
         <v>45907</v>
       </c>
@@ -34522,7 +34571,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="10">
         <v>45914</v>
       </c>
@@ -34557,7 +34606,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="10">
         <v>45921</v>
       </c>
@@ -34592,7 +34641,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="10">
         <v>45928</v>
       </c>
@@ -34627,7 +34676,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="10">
         <v>45935</v>
       </c>
@@ -34662,7 +34711,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="10">
         <v>45942</v>
       </c>
@@ -34697,7 +34746,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="10">
         <v>45949</v>
       </c>
@@ -34732,7 +34781,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="10">
         <v>45956</v>
       </c>
@@ -34767,7 +34816,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="10">
         <v>45963</v>
       </c>
@@ -34802,7 +34851,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="10">
         <v>45970</v>
       </c>
@@ -34837,7 +34886,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="10">
         <v>45977</v>
       </c>
@@ -34872,7 +34921,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="10">
         <v>45984</v>
       </c>
@@ -34907,7 +34956,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="10">
         <v>45991</v>
       </c>
@@ -34942,7 +34991,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="10">
         <v>45998</v>
       </c>
@@ -34977,7 +35026,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="10">
         <v>46005</v>
       </c>
@@ -35012,7 +35061,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="10">
         <v>46012</v>
       </c>
@@ -35047,7 +35096,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="10">
         <v>46026</v>
       </c>
@@ -35082,7 +35131,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="10">
         <v>46033</v>
       </c>
@@ -35117,7 +35166,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="10">
         <v>46040</v>
       </c>
@@ -35152,7 +35201,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="10">
         <v>46047</v>
       </c>
@@ -35187,7 +35236,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="10">
         <v>46054</v>
       </c>
@@ -35222,7 +35271,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="10">
         <v>46061</v>
       </c>
@@ -35257,7 +35306,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="10">
         <v>46068</v>
       </c>
@@ -35292,7 +35341,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="10">
         <v>46075</v>
       </c>
@@ -35327,7 +35376,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="10">
         <v>46082</v>
       </c>
@@ -35362,7 +35411,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="10">
         <v>46089</v>
       </c>
@@ -35397,7 +35446,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="10">
         <v>46096</v>
       </c>
@@ -35432,7 +35481,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="10">
         <v>46103</v>
       </c>
@@ -35467,7 +35516,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" s="10">
         <v>46110</v>
       </c>
@@ -35502,7 +35551,7 @@
         <v>5348</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="10">
         <v>46117</v>
       </c>
@@ -35537,7 +35586,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="10">
         <v>46124</v>
       </c>
@@ -35572,7 +35621,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="10">
         <v>46131</v>
       </c>
@@ -35607,7 +35656,7 @@
         <v>5837</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="10">
         <v>46138</v>
       </c>
@@ -35642,7 +35691,7 @@
         <v>5881</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="10">
         <v>46145</v>
       </c>
@@ -35677,7 +35726,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="10">
         <v>46152</v>
       </c>
@@ -35712,7 +35761,7 @@
         <v>5909</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="10">
         <v>46159</v>
       </c>
@@ -35747,7 +35796,7 @@
         <v>5807</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="10">
         <v>46166</v>
       </c>
@@ -35782,7 +35831,7 @@
         <v>5932</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" s="10">
         <v>46173</v>
       </c>
@@ -35817,7 +35866,7 @@
         <v>5984</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="10">
         <v>46180</v>
       </c>
@@ -35852,7 +35901,7 @@
         <v>6121</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="10">
         <v>46187</v>
       </c>
@@ -35887,7 +35936,7 @@
         <v>6025</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="10">
         <v>46194</v>
       </c>
@@ -35922,7 +35971,7 @@
         <v>6239</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="10">
         <v>46201</v>
       </c>
@@ -35955,6 +36004,41 @@
       </c>
       <c r="K444" s="13">
         <v>5992</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A445" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B445" s="11">
+        <v>46209</v>
+      </c>
+      <c r="C445" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D445" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E445" s="13">
+        <v>2551</v>
+      </c>
+      <c r="F445" s="13">
+        <v>1171</v>
+      </c>
+      <c r="G445" s="13">
+        <v>4412</v>
+      </c>
+      <c r="H445" s="13">
+        <v>1065</v>
+      </c>
+      <c r="I445" s="13">
+        <v>1349</v>
+      </c>
+      <c r="J445" s="13">
+        <v>275</v>
+      </c>
+      <c r="K445" s="13">
+        <v>5634</v>
       </c>
     </row>
   </sheetData>
@@ -35968,7 +36052,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
@@ -35984,12 +36068,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15.6">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
@@ -36001,7 +36085,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650EFCDA-CBD8-4531-A845-12DDA50F8C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C22B23-1403-4FCB-8AF3-A4DC23B1C67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -109,29 +109,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -153,7 +153,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -170,7 +170,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -214,7 +214,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -235,33 +235,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -279,7 +279,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1660,6 +1660,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3000,6 +3003,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>2551</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>2486</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4375,6 +4381,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5715,6 +5724,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>1171</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>1165</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7090,6 +7102,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8430,6 +8445,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>4412</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4280</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9805,6 +9823,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11145,6 +11166,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>1065</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>1164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12520,6 +12544,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13860,6 +13887,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>1349</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>1134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15237,6 +15267,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16577,6 +16610,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>5634</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>5533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17968,6 +18004,9 @@
                 <c:pt idx="443">
                   <c:v>46209</c:v>
                 </c:pt>
+                <c:pt idx="444">
+                  <c:v>46216</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19308,6 +19347,9 @@
                 </c:pt>
                 <c:pt idx="443">
                   <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>311</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20454,19 +20496,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K445"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K446"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="7.19921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="7.1796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
@@ -20501,7 +20543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="10">
         <v>43100</v>
       </c>
@@ -20536,7 +20578,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="10">
         <v>43107</v>
       </c>
@@ -20571,7 +20613,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4" s="10">
         <v>43114</v>
       </c>
@@ -20606,7 +20648,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="10">
         <v>43121</v>
       </c>
@@ -20641,7 +20683,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="10">
         <v>43128</v>
       </c>
@@ -20676,7 +20718,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7" s="10">
         <v>43135</v>
       </c>
@@ -20711,7 +20753,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" s="10">
         <v>43142</v>
       </c>
@@ -20746,7 +20788,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" s="10">
         <v>43149</v>
       </c>
@@ -20781,7 +20823,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" s="10">
         <v>43156</v>
       </c>
@@ -20816,7 +20858,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="10">
         <v>43163</v>
       </c>
@@ -20851,7 +20893,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" s="10">
         <v>43170</v>
       </c>
@@ -20886,7 +20928,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" s="10">
         <v>43177</v>
       </c>
@@ -20921,7 +20963,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14" s="10">
         <v>43184</v>
       </c>
@@ -20956,7 +20998,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15" s="10">
         <v>43191</v>
       </c>
@@ -20991,7 +21033,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="10">
         <v>43198</v>
       </c>
@@ -21026,7 +21068,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
         <v>43205</v>
       </c>
@@ -21061,7 +21103,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
         <v>43212</v>
       </c>
@@ -21096,7 +21138,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
         <v>43219</v>
       </c>
@@ -21131,7 +21173,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
         <v>43226</v>
       </c>
@@ -21166,7 +21208,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
         <v>43233</v>
       </c>
@@ -21201,7 +21243,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
         <v>43240</v>
       </c>
@@ -21236,7 +21278,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
         <v>43247</v>
       </c>
@@ -21271,7 +21313,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
         <v>43254</v>
       </c>
@@ -21306,7 +21348,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
         <v>43261</v>
       </c>
@@ -21341,7 +21383,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
         <v>43268</v>
       </c>
@@ -21376,7 +21418,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
         <v>43275</v>
       </c>
@@ -21411,7 +21453,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
         <v>43282</v>
       </c>
@@ -21446,7 +21488,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
         <v>43289</v>
       </c>
@@ -21481,7 +21523,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
         <v>43296</v>
       </c>
@@ -21516,7 +21558,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
         <v>43303</v>
       </c>
@@ -21551,7 +21593,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
         <v>43310</v>
       </c>
@@ -21586,7 +21628,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
         <v>43317</v>
       </c>
@@ -21621,7 +21663,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34" s="10">
         <v>43324</v>
       </c>
@@ -21656,7 +21698,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="10">
         <v>43331</v>
       </c>
@@ -21691,7 +21733,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36" s="10">
         <v>43338</v>
       </c>
@@ -21726,7 +21768,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="10">
         <v>43345</v>
       </c>
@@ -21761,7 +21803,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38" s="10">
         <v>43352</v>
       </c>
@@ -21796,7 +21838,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" s="10">
         <v>43359</v>
       </c>
@@ -21831,7 +21873,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40" s="10">
         <v>43366</v>
       </c>
@@ -21866,7 +21908,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41" s="10">
         <v>43373</v>
       </c>
@@ -21901,7 +21943,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42" s="10">
         <v>43380</v>
       </c>
@@ -21936,7 +21978,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43" s="10">
         <v>43387</v>
       </c>
@@ -21971,7 +22013,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44" s="10">
         <v>43394</v>
       </c>
@@ -22006,7 +22048,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45" s="10">
         <v>43401</v>
       </c>
@@ -22041,7 +22083,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46" s="10">
         <v>43408</v>
       </c>
@@ -22076,7 +22118,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47" s="10">
         <v>43415</v>
       </c>
@@ -22111,7 +22153,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48" s="10">
         <v>43422</v>
       </c>
@@ -22146,7 +22188,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49" s="10">
         <v>43429</v>
       </c>
@@ -22181,7 +22223,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11">
       <c r="A50" s="10">
         <v>43436</v>
       </c>
@@ -22216,7 +22258,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11">
       <c r="A51" s="10">
         <v>43443</v>
       </c>
@@ -22251,7 +22293,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11">
       <c r="A52" s="10">
         <v>43450</v>
       </c>
@@ -22286,7 +22328,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11">
       <c r="A53" s="10">
         <v>43457</v>
       </c>
@@ -22321,7 +22363,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11">
       <c r="A54" s="10">
         <v>43464</v>
       </c>
@@ -22356,7 +22398,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11">
       <c r="A55" s="10">
         <v>43471</v>
       </c>
@@ -22391,7 +22433,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11">
       <c r="A56" s="10">
         <v>43478</v>
       </c>
@@ -22426,7 +22468,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11">
       <c r="A57" s="10">
         <v>43485</v>
       </c>
@@ -22461,7 +22503,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11">
       <c r="A58" s="10">
         <v>43492</v>
       </c>
@@ -22496,7 +22538,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11">
       <c r="A59" s="10">
         <v>43499</v>
       </c>
@@ -22531,7 +22573,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11">
       <c r="A60" s="10">
         <v>43506</v>
       </c>
@@ -22566,7 +22608,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11">
       <c r="A61" s="10">
         <v>43513</v>
       </c>
@@ -22601,7 +22643,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11">
       <c r="A62" s="10">
         <v>43520</v>
       </c>
@@ -22636,7 +22678,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11">
       <c r="A63" s="10">
         <v>43527</v>
       </c>
@@ -22671,7 +22713,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11">
       <c r="A64" s="10">
         <v>43534</v>
       </c>
@@ -22706,7 +22748,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11">
       <c r="A65" s="10">
         <v>43541</v>
       </c>
@@ -22741,7 +22783,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11">
       <c r="A66" s="10">
         <v>43548</v>
       </c>
@@ -22776,7 +22818,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
       <c r="A67" s="10">
         <v>43555</v>
       </c>
@@ -22811,7 +22853,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
       <c r="A68" s="10">
         <v>43562</v>
       </c>
@@ -22846,7 +22888,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11">
       <c r="A69" s="10">
         <v>43569</v>
       </c>
@@ -22881,7 +22923,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="A70" s="10">
         <v>43576</v>
       </c>
@@ -22916,7 +22958,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="A71" s="10">
         <v>43583</v>
       </c>
@@ -22951,7 +22993,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="A72" s="10">
         <v>43590</v>
       </c>
@@ -22986,7 +23028,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11">
       <c r="A73" s="10">
         <v>43597</v>
       </c>
@@ -23021,7 +23063,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11">
       <c r="A74" s="10">
         <v>43604</v>
       </c>
@@ -23056,7 +23098,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11">
       <c r="A75" s="10">
         <v>43611</v>
       </c>
@@ -23091,7 +23133,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11">
       <c r="A76" s="10">
         <v>43618</v>
       </c>
@@ -23126,7 +23168,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11">
       <c r="A77" s="10">
         <v>43625</v>
       </c>
@@ -23161,7 +23203,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11">
       <c r="A78" s="10">
         <v>43632</v>
       </c>
@@ -23196,7 +23238,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11">
       <c r="A79" s="10">
         <v>43639</v>
       </c>
@@ -23231,7 +23273,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="A80" s="10">
         <v>43646</v>
       </c>
@@ -23266,7 +23308,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11">
       <c r="A81" s="10">
         <v>43653</v>
       </c>
@@ -23301,7 +23343,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11">
       <c r="A82" s="10">
         <v>43660</v>
       </c>
@@ -23336,7 +23378,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11">
       <c r="A83" s="10">
         <v>43667</v>
       </c>
@@ -23371,7 +23413,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11">
       <c r="A84" s="10">
         <v>43674</v>
       </c>
@@ -23406,7 +23448,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11">
       <c r="A85" s="10">
         <v>43681</v>
       </c>
@@ -23441,7 +23483,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11">
       <c r="A86" s="10">
         <v>43688</v>
       </c>
@@ -23476,7 +23518,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11">
       <c r="A87" s="10">
         <v>43695</v>
       </c>
@@ -23511,7 +23553,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11">
       <c r="A88" s="10">
         <v>43702</v>
       </c>
@@ -23546,7 +23588,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11">
       <c r="A89" s="10">
         <v>43709</v>
       </c>
@@ -23581,7 +23623,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11">
       <c r="A90" s="10">
         <v>43716</v>
       </c>
@@ -23616,7 +23658,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11">
       <c r="A91" s="10">
         <v>43723</v>
       </c>
@@ -23651,7 +23693,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11">
       <c r="A92" s="10">
         <v>43730</v>
       </c>
@@ -23686,7 +23728,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11">
       <c r="A93" s="10">
         <v>43737</v>
       </c>
@@ -23721,7 +23763,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11">
       <c r="A94" s="10">
         <v>43744</v>
       </c>
@@ -23756,7 +23798,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11">
       <c r="A95" s="10">
         <v>43751</v>
       </c>
@@ -23791,7 +23833,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11">
       <c r="A96" s="10">
         <v>43758</v>
       </c>
@@ -23826,7 +23868,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11">
       <c r="A97" s="10">
         <v>43765</v>
       </c>
@@ -23861,7 +23903,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11">
       <c r="A98" s="10">
         <v>43772</v>
       </c>
@@ -23896,7 +23938,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11">
       <c r="A99" s="10">
         <v>43779</v>
       </c>
@@ -23931,7 +23973,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11">
       <c r="A100" s="10">
         <v>43786</v>
       </c>
@@ -23966,7 +24008,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11">
       <c r="A101" s="10">
         <v>43793</v>
       </c>
@@ -24001,7 +24043,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11">
       <c r="A102" s="10">
         <v>43800</v>
       </c>
@@ -24036,7 +24078,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11">
       <c r="A103" s="10">
         <v>43807</v>
       </c>
@@ -24071,7 +24113,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11">
       <c r="A104" s="10">
         <v>43814</v>
       </c>
@@ -24106,7 +24148,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11">
       <c r="A105" s="10">
         <v>43821</v>
       </c>
@@ -24141,7 +24183,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11">
       <c r="A106" s="10">
         <v>43828</v>
       </c>
@@ -24176,7 +24218,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11">
       <c r="A107" s="10">
         <v>43835</v>
       </c>
@@ -24211,7 +24253,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11">
       <c r="A108" s="10">
         <v>43842</v>
       </c>
@@ -24246,7 +24288,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11">
       <c r="A109" s="10">
         <v>43849</v>
       </c>
@@ -24281,7 +24323,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11">
       <c r="A110" s="10">
         <v>43856</v>
       </c>
@@ -24316,7 +24358,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11">
       <c r="A111" s="10">
         <v>43863</v>
       </c>
@@ -24351,7 +24393,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11">
       <c r="A112" s="10">
         <v>43870</v>
       </c>
@@ -24386,7 +24428,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11">
       <c r="A113" s="10">
         <v>43877</v>
       </c>
@@ -24421,7 +24463,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11">
       <c r="A114" s="10">
         <v>43884</v>
       </c>
@@ -24456,7 +24498,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11">
       <c r="A115" s="10">
         <v>43891</v>
       </c>
@@ -24491,7 +24533,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11">
       <c r="A116" s="10">
         <v>43898</v>
       </c>
@@ -24526,7 +24568,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11">
       <c r="A117" s="10">
         <v>43905</v>
       </c>
@@ -24561,7 +24603,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11">
       <c r="A118" s="10">
         <v>43912</v>
       </c>
@@ -24596,7 +24638,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11">
       <c r="A119" s="10">
         <v>43919</v>
       </c>
@@ -24631,7 +24673,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11">
       <c r="A120" s="10">
         <v>43926</v>
       </c>
@@ -24666,7 +24708,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11">
       <c r="A121" s="10">
         <v>43933</v>
       </c>
@@ -24701,7 +24743,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11">
       <c r="A122" s="10">
         <v>43940</v>
       </c>
@@ -24736,7 +24778,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11">
       <c r="A123" s="10">
         <v>43947</v>
       </c>
@@ -24771,7 +24813,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11">
       <c r="A124" s="10">
         <v>43954</v>
       </c>
@@ -24806,7 +24848,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11">
       <c r="A125" s="10">
         <v>43961</v>
       </c>
@@ -24841,7 +24883,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11">
       <c r="A126" s="10">
         <v>43968</v>
       </c>
@@ -24876,7 +24918,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11">
       <c r="A127" s="10">
         <v>43975</v>
       </c>
@@ -24911,7 +24953,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11">
       <c r="A128" s="10">
         <v>43982</v>
       </c>
@@ -24946,7 +24988,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11">
       <c r="A129" s="10">
         <v>43989</v>
       </c>
@@ -24981,7 +25023,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11">
       <c r="A130" s="10">
         <v>43996</v>
       </c>
@@ -25016,7 +25058,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11">
       <c r="A131" s="10">
         <v>44003</v>
       </c>
@@ -25051,7 +25093,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11">
       <c r="A132" s="10">
         <v>44010</v>
       </c>
@@ -25086,7 +25128,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11">
       <c r="A133" s="10">
         <v>44017</v>
       </c>
@@ -25121,7 +25163,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11">
       <c r="A134" s="10">
         <v>44024</v>
       </c>
@@ -25156,7 +25198,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11">
       <c r="A135" s="10">
         <v>44031</v>
       </c>
@@ -25191,7 +25233,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11">
       <c r="A136" s="10">
         <v>44038</v>
       </c>
@@ -25226,7 +25268,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11">
       <c r="A137" s="10">
         <v>44045</v>
       </c>
@@ -25261,7 +25303,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11">
       <c r="A138" s="10">
         <v>44052</v>
       </c>
@@ -25296,7 +25338,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11">
       <c r="A139" s="10">
         <v>44059</v>
       </c>
@@ -25331,7 +25373,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11">
       <c r="A140" s="10">
         <v>44066</v>
       </c>
@@ -25366,7 +25408,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11">
       <c r="A141" s="10">
         <v>44073</v>
       </c>
@@ -25401,7 +25443,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11">
       <c r="A142" s="10">
         <v>44080</v>
       </c>
@@ -25436,7 +25478,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11">
       <c r="A143" s="10">
         <v>44087</v>
       </c>
@@ -25471,7 +25513,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11">
       <c r="A144" s="10">
         <v>44094</v>
       </c>
@@ -25506,7 +25548,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11">
       <c r="A145" s="10">
         <v>44101</v>
       </c>
@@ -25541,7 +25583,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11">
       <c r="A146" s="10">
         <v>44108</v>
       </c>
@@ -25576,7 +25618,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11">
       <c r="A147" s="10">
         <v>44115</v>
       </c>
@@ -25611,7 +25653,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11">
       <c r="A148" s="10">
         <v>44122</v>
       </c>
@@ -25646,7 +25688,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11">
       <c r="A149" s="10">
         <v>44129</v>
       </c>
@@ -25681,7 +25723,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11">
       <c r="A150" s="10">
         <v>44136</v>
       </c>
@@ -25716,7 +25758,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11">
       <c r="A151" s="10">
         <v>44143</v>
       </c>
@@ -25751,7 +25793,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11">
       <c r="A152" s="10">
         <v>44150</v>
       </c>
@@ -25786,7 +25828,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11">
       <c r="A153" s="10">
         <v>44157</v>
       </c>
@@ -25821,7 +25863,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11">
       <c r="A154" s="10">
         <v>44164</v>
       </c>
@@ -25856,7 +25898,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11">
       <c r="A155" s="10">
         <v>44171</v>
       </c>
@@ -25891,7 +25933,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11">
       <c r="A156" s="10">
         <v>44178</v>
       </c>
@@ -25926,7 +25968,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11">
       <c r="A157" s="10">
         <v>44185</v>
       </c>
@@ -25961,7 +26003,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11">
       <c r="A158" s="10">
         <v>44192</v>
       </c>
@@ -25996,7 +26038,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11">
       <c r="A159" s="10">
         <v>44199</v>
       </c>
@@ -26031,7 +26073,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11">
       <c r="A160" s="10">
         <v>44206</v>
       </c>
@@ -26066,7 +26108,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11">
       <c r="A161" s="10">
         <v>44213</v>
       </c>
@@ -26101,7 +26143,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11">
       <c r="A162" s="10">
         <v>44220</v>
       </c>
@@ -26136,7 +26178,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11">
       <c r="A163" s="10">
         <v>44227</v>
       </c>
@@ -26171,7 +26213,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11">
       <c r="A164" s="10">
         <v>44234</v>
       </c>
@@ -26206,7 +26248,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11">
       <c r="A165" s="10">
         <v>44241</v>
       </c>
@@ -26241,7 +26283,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11">
       <c r="A166" s="10">
         <v>44248</v>
       </c>
@@ -26276,7 +26318,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11">
       <c r="A167" s="10">
         <v>44255</v>
       </c>
@@ -26311,7 +26353,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11">
       <c r="A168" s="10">
         <v>44262</v>
       </c>
@@ -26346,7 +26388,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11">
       <c r="A169" s="10">
         <v>44269</v>
       </c>
@@ -26381,7 +26423,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11">
       <c r="A170" s="10">
         <v>44276</v>
       </c>
@@ -26416,7 +26458,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11">
       <c r="A171" s="10">
         <v>44283</v>
       </c>
@@ -26451,7 +26493,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11">
       <c r="A172" s="10">
         <v>44290</v>
       </c>
@@ -26486,7 +26528,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11">
       <c r="A173" s="10">
         <v>44297</v>
       </c>
@@ -26521,7 +26563,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11">
       <c r="A174" s="10">
         <v>44304</v>
       </c>
@@ -26556,7 +26598,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11">
       <c r="A175" s="10">
         <v>44311</v>
       </c>
@@ -26591,7 +26633,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11">
       <c r="A176" s="10">
         <v>44318</v>
       </c>
@@ -26626,7 +26668,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11">
       <c r="A177" s="10">
         <v>44325</v>
       </c>
@@ -26661,7 +26703,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11">
       <c r="A178" s="10">
         <v>44332</v>
       </c>
@@ -26696,7 +26738,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11">
       <c r="A179" s="10">
         <v>44339</v>
       </c>
@@ -26731,7 +26773,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11">
       <c r="A180" s="10">
         <v>44346</v>
       </c>
@@ -26766,7 +26808,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11">
       <c r="A181" s="10">
         <v>44353</v>
       </c>
@@ -26801,7 +26843,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11">
       <c r="A182" s="10">
         <v>44360</v>
       </c>
@@ -26836,7 +26878,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11">
       <c r="A183" s="10">
         <v>44367</v>
       </c>
@@ -26871,7 +26913,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11">
       <c r="A184" s="10">
         <v>44374</v>
       </c>
@@ -26906,7 +26948,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11">
       <c r="A185" s="10">
         <v>44381</v>
       </c>
@@ -26941,7 +26983,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11">
       <c r="A186" s="10">
         <v>44388</v>
       </c>
@@ -26976,7 +27018,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11">
       <c r="A187" s="10">
         <v>44395</v>
       </c>
@@ -27011,7 +27053,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11">
       <c r="A188" s="10">
         <v>44402</v>
       </c>
@@ -27046,7 +27088,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11">
       <c r="A189" s="10">
         <v>44409</v>
       </c>
@@ -27081,7 +27123,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11">
       <c r="A190" s="10">
         <v>44416</v>
       </c>
@@ -27116,7 +27158,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11">
       <c r="A191" s="10">
         <v>44423</v>
       </c>
@@ -27151,7 +27193,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11">
       <c r="A192" s="10">
         <v>44430</v>
       </c>
@@ -27186,7 +27228,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11">
       <c r="A193" s="10">
         <v>44437</v>
       </c>
@@ -27221,7 +27263,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11">
       <c r="A194" s="10">
         <v>44444</v>
       </c>
@@ -27256,7 +27298,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11">
       <c r="A195" s="10">
         <v>44451</v>
       </c>
@@ -27291,7 +27333,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11">
       <c r="A196" s="10">
         <v>44458</v>
       </c>
@@ -27326,7 +27368,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11">
       <c r="A197" s="10">
         <v>44465</v>
       </c>
@@ -27361,7 +27403,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11">
       <c r="A198" s="10">
         <v>44472</v>
       </c>
@@ -27396,7 +27438,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11">
       <c r="A199" s="10">
         <v>44479</v>
       </c>
@@ -27431,7 +27473,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11">
       <c r="A200" s="10">
         <v>44486</v>
       </c>
@@ -27466,7 +27508,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11">
       <c r="A201" s="10">
         <v>44493</v>
       </c>
@@ -27501,7 +27543,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11">
       <c r="A202" s="10">
         <v>44500</v>
       </c>
@@ -27536,7 +27578,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11">
       <c r="A203" s="10">
         <v>44507</v>
       </c>
@@ -27571,7 +27613,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11">
       <c r="A204" s="10">
         <v>44514</v>
       </c>
@@ -27606,7 +27648,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11">
       <c r="A205" s="10">
         <v>44521</v>
       </c>
@@ -27641,7 +27683,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11">
       <c r="A206" s="10">
         <v>44528</v>
       </c>
@@ -27676,7 +27718,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11">
       <c r="A207" s="10">
         <v>44535</v>
       </c>
@@ -27711,7 +27753,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11">
       <c r="A208" s="10">
         <v>44542</v>
       </c>
@@ -27746,7 +27788,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11">
       <c r="A209" s="10">
         <v>44549</v>
       </c>
@@ -27781,7 +27823,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11">
       <c r="A210" s="10">
         <v>44556</v>
       </c>
@@ -27816,7 +27858,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11">
       <c r="A211" s="10">
         <v>44563</v>
       </c>
@@ -27851,7 +27893,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11">
       <c r="A212" s="10">
         <v>44570</v>
       </c>
@@ -27886,7 +27928,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11">
       <c r="A213" s="10">
         <v>44577</v>
       </c>
@@ -27921,7 +27963,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11">
       <c r="A214" s="10">
         <v>44584</v>
       </c>
@@ -27956,7 +27998,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11">
       <c r="A215" s="10">
         <v>44591</v>
       </c>
@@ -27991,7 +28033,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11">
       <c r="A216" s="10">
         <v>44598</v>
       </c>
@@ -28026,7 +28068,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11">
       <c r="A217" s="10">
         <v>44605</v>
       </c>
@@ -28061,7 +28103,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11">
       <c r="A218" s="10">
         <v>44612</v>
       </c>
@@ -28096,7 +28138,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11">
       <c r="A219" s="10">
         <v>44619</v>
       </c>
@@ -28131,7 +28173,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11">
       <c r="A220" s="10">
         <v>44626</v>
       </c>
@@ -28166,7 +28208,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11">
       <c r="A221" s="10">
         <v>44633</v>
       </c>
@@ -28201,7 +28243,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11">
       <c r="A222" s="10">
         <v>44640</v>
       </c>
@@ -28236,7 +28278,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11">
       <c r="A223" s="10">
         <v>44647</v>
       </c>
@@ -28271,7 +28313,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11">
       <c r="A224" s="10">
         <v>44654</v>
       </c>
@@ -28306,7 +28348,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11">
       <c r="A225" s="10">
         <v>44661</v>
       </c>
@@ -28341,7 +28383,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11">
       <c r="A226" s="10">
         <v>44668</v>
       </c>
@@ -28376,7 +28418,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11">
       <c r="A227" s="10">
         <v>44675</v>
       </c>
@@ -28411,7 +28453,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11">
       <c r="A228" s="10">
         <v>44682</v>
       </c>
@@ -28446,7 +28488,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11">
       <c r="A229" s="10">
         <v>44689</v>
       </c>
@@ -28481,7 +28523,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11">
       <c r="A230" s="10">
         <v>44696</v>
       </c>
@@ -28516,7 +28558,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11">
       <c r="A231" s="10">
         <v>44703</v>
       </c>
@@ -28551,7 +28593,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11">
       <c r="A232" s="10">
         <v>44710</v>
       </c>
@@ -28586,7 +28628,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11">
       <c r="A233" s="10">
         <v>44717</v>
       </c>
@@ -28621,7 +28663,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11">
       <c r="A234" s="10">
         <v>44724</v>
       </c>
@@ -28656,7 +28698,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11">
       <c r="A235" s="10">
         <v>44731</v>
       </c>
@@ -28691,7 +28733,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11">
       <c r="A236" s="10">
         <v>44738</v>
       </c>
@@ -28726,7 +28768,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11">
       <c r="A237" s="10">
         <v>44745</v>
       </c>
@@ -28761,7 +28803,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11">
       <c r="A238" s="10">
         <v>44752</v>
       </c>
@@ -28796,7 +28838,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11">
       <c r="A239" s="10">
         <v>44759</v>
       </c>
@@ -28831,7 +28873,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11">
       <c r="A240" s="10">
         <v>44766</v>
       </c>
@@ -28866,7 +28908,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11">
       <c r="A241" s="10">
         <v>44773</v>
       </c>
@@ -28901,7 +28943,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11">
       <c r="A242" s="10">
         <v>44780</v>
       </c>
@@ -28936,7 +28978,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11">
       <c r="A243" s="10">
         <v>44787</v>
       </c>
@@ -28971,7 +29013,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11">
       <c r="A244" s="10">
         <v>44794</v>
       </c>
@@ -29006,7 +29048,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11">
       <c r="A245" s="10">
         <v>44801</v>
       </c>
@@ -29041,7 +29083,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11">
       <c r="A246" s="10">
         <v>44808</v>
       </c>
@@ -29076,7 +29118,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11">
       <c r="A247" s="10">
         <v>44815</v>
       </c>
@@ -29111,7 +29153,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11">
       <c r="A248" s="10">
         <v>44822</v>
       </c>
@@ -29146,7 +29188,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11">
       <c r="A249" s="10">
         <v>44829</v>
       </c>
@@ -29181,7 +29223,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11">
       <c r="A250" s="10">
         <v>44836</v>
       </c>
@@ -29216,7 +29258,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11">
       <c r="A251" s="10">
         <v>44843</v>
       </c>
@@ -29251,7 +29293,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11">
       <c r="A252" s="10">
         <v>44850</v>
       </c>
@@ -29286,7 +29328,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11">
       <c r="A253" s="10">
         <v>44857</v>
       </c>
@@ -29321,7 +29363,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11">
       <c r="A254" s="10">
         <v>44864</v>
       </c>
@@ -29356,7 +29398,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11">
       <c r="A255" s="10">
         <v>44871</v>
       </c>
@@ -29391,7 +29433,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11">
       <c r="A256" s="10">
         <v>44878</v>
       </c>
@@ -29426,7 +29468,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11">
       <c r="A257" s="10">
         <v>44885</v>
       </c>
@@ -29461,7 +29503,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11">
       <c r="A258" s="10">
         <v>44892</v>
       </c>
@@ -29496,7 +29538,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11">
       <c r="A259" s="10">
         <v>44899</v>
       </c>
@@ -29531,7 +29573,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11">
       <c r="A260" s="10">
         <v>44906</v>
       </c>
@@ -29566,7 +29608,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11">
       <c r="A261" s="10">
         <v>44913</v>
       </c>
@@ -29601,7 +29643,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11">
       <c r="A262" s="10">
         <v>44920</v>
       </c>
@@ -29636,7 +29678,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11">
       <c r="A263" s="10">
         <v>44927</v>
       </c>
@@ -29671,7 +29713,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11">
       <c r="A264" s="10">
         <v>44934</v>
       </c>
@@ -29706,7 +29748,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11">
       <c r="A265" s="10">
         <v>44941</v>
       </c>
@@ -29741,7 +29783,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11">
       <c r="A266" s="10">
         <v>44948</v>
       </c>
@@ -29776,7 +29818,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11">
       <c r="A267" s="10">
         <v>44955</v>
       </c>
@@ -29811,7 +29853,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11">
       <c r="A268" s="10">
         <v>44962</v>
       </c>
@@ -29846,7 +29888,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11">
       <c r="A269" s="10">
         <v>44969</v>
       </c>
@@ -29881,7 +29923,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11">
       <c r="A270" s="10">
         <v>44976</v>
       </c>
@@ -29916,7 +29958,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11">
       <c r="A271" s="10">
         <v>44983</v>
       </c>
@@ -29951,7 +29993,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11">
       <c r="A272" s="10">
         <v>44990</v>
       </c>
@@ -29986,7 +30028,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11">
       <c r="A273" s="10">
         <v>44997</v>
       </c>
@@ -30021,7 +30063,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11">
       <c r="A274" s="10">
         <v>45004</v>
       </c>
@@ -30056,7 +30098,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11">
       <c r="A275" s="10">
         <v>45011</v>
       </c>
@@ -30091,7 +30133,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11">
       <c r="A276" s="10">
         <v>45018</v>
       </c>
@@ -30126,7 +30168,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11">
       <c r="A277" s="10">
         <v>45025</v>
       </c>
@@ -30161,7 +30203,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11">
       <c r="A278" s="10">
         <v>45032</v>
       </c>
@@ -30196,7 +30238,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11">
       <c r="A279" s="10">
         <v>45039</v>
       </c>
@@ -30231,7 +30273,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11">
       <c r="A280" s="10">
         <v>45046</v>
       </c>
@@ -30266,7 +30308,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11">
       <c r="A281" s="10">
         <v>45053</v>
       </c>
@@ -30301,7 +30343,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11">
       <c r="A282" s="10">
         <v>45060</v>
       </c>
@@ -30336,7 +30378,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11">
       <c r="A283" s="10">
         <v>45067</v>
       </c>
@@ -30371,7 +30413,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11">
       <c r="A284" s="10">
         <v>45074</v>
       </c>
@@ -30406,7 +30448,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11">
       <c r="A285" s="10">
         <v>45081</v>
       </c>
@@ -30441,7 +30483,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11">
       <c r="A286" s="10">
         <v>45088</v>
       </c>
@@ -30476,7 +30518,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11">
       <c r="A287" s="10">
         <v>45095</v>
       </c>
@@ -30511,7 +30553,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11">
       <c r="A288" s="10">
         <v>45102</v>
       </c>
@@ -30546,7 +30588,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11">
       <c r="A289" s="10">
         <v>45109</v>
       </c>
@@ -30581,7 +30623,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11">
       <c r="A290" s="10">
         <v>45116</v>
       </c>
@@ -30616,7 +30658,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11">
       <c r="A291" s="10">
         <v>45123</v>
       </c>
@@ -30651,7 +30693,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11">
       <c r="A292" s="10">
         <v>45130</v>
       </c>
@@ -30686,7 +30728,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11">
       <c r="A293" s="10">
         <v>45137</v>
       </c>
@@ -30721,7 +30763,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11">
       <c r="A294" s="10">
         <v>45144</v>
       </c>
@@ -30756,7 +30798,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11">
       <c r="A295" s="10">
         <v>45151</v>
       </c>
@@ -30791,7 +30833,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11">
       <c r="A296" s="10">
         <v>45158</v>
       </c>
@@ -30826,7 +30868,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11">
       <c r="A297" s="10">
         <v>45165</v>
       </c>
@@ -30861,7 +30903,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11">
       <c r="A298" s="10">
         <v>45172</v>
       </c>
@@ -30896,7 +30938,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11">
       <c r="A299" s="10">
         <v>45179</v>
       </c>
@@ -30931,7 +30973,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11">
       <c r="A300" s="10">
         <v>45186</v>
       </c>
@@ -30966,7 +31008,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11">
       <c r="A301" s="10">
         <v>45193</v>
       </c>
@@ -31001,7 +31043,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11">
       <c r="A302" s="10">
         <v>45200</v>
       </c>
@@ -31036,7 +31078,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11">
       <c r="A303" s="10">
         <v>45207</v>
       </c>
@@ -31071,7 +31113,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11">
       <c r="A304" s="10">
         <v>45214</v>
       </c>
@@ -31106,7 +31148,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11">
       <c r="A305" s="10">
         <v>45221</v>
       </c>
@@ -31141,7 +31183,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11">
       <c r="A306" s="10">
         <v>45228</v>
       </c>
@@ -31176,7 +31218,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11">
       <c r="A307" s="10">
         <v>45235</v>
       </c>
@@ -31211,7 +31253,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11">
       <c r="A308" s="10">
         <v>45242</v>
       </c>
@@ -31246,7 +31288,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11">
       <c r="A309" s="10">
         <v>45249</v>
       </c>
@@ -31281,7 +31323,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11">
       <c r="A310" s="10">
         <v>45256</v>
       </c>
@@ -31316,7 +31358,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11">
       <c r="A311" s="10">
         <v>45263</v>
       </c>
@@ -31351,7 +31393,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11">
       <c r="A312" s="10">
         <v>45270</v>
       </c>
@@ -31386,7 +31428,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11">
       <c r="A313" s="10">
         <v>45277</v>
       </c>
@@ -31421,7 +31463,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11">
       <c r="A314" s="10">
         <v>45284</v>
       </c>
@@ -31456,7 +31498,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11">
       <c r="A315" s="10">
         <v>45291</v>
       </c>
@@ -31491,7 +31533,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11">
       <c r="A316" s="10">
         <v>45298</v>
       </c>
@@ -31526,7 +31568,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11">
       <c r="A317" s="10">
         <v>45305</v>
       </c>
@@ -31561,7 +31603,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11">
       <c r="A318" s="10">
         <v>45312</v>
       </c>
@@ -31596,7 +31638,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11">
       <c r="A319" s="10">
         <v>45319</v>
       </c>
@@ -31631,7 +31673,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11">
       <c r="A320" s="10">
         <v>45326</v>
       </c>
@@ -31666,7 +31708,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11">
       <c r="A321" s="10">
         <v>45333</v>
       </c>
@@ -31701,7 +31743,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11">
       <c r="A322" s="10">
         <v>45340</v>
       </c>
@@ -31736,7 +31778,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11">
       <c r="A323" s="10">
         <v>45347</v>
       </c>
@@ -31771,7 +31813,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11">
       <c r="A324" s="10">
         <v>45354</v>
       </c>
@@ -31806,7 +31848,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11">
       <c r="A325" s="10">
         <v>45361</v>
       </c>
@@ -31841,7 +31883,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11">
       <c r="A326" s="10">
         <v>45368</v>
       </c>
@@ -31876,7 +31918,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11">
       <c r="A327" s="10">
         <v>45375</v>
       </c>
@@ -31911,7 +31953,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11">
       <c r="A328" s="10">
         <v>45382</v>
       </c>
@@ -31946,7 +31988,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11">
       <c r="A329" s="10">
         <v>45389</v>
       </c>
@@ -31981,7 +32023,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11">
       <c r="A330" s="10">
         <v>45396</v>
       </c>
@@ -32016,7 +32058,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11">
       <c r="A331" s="10">
         <v>45403</v>
       </c>
@@ -32051,7 +32093,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11">
       <c r="A332" s="10">
         <v>45410</v>
       </c>
@@ -32086,7 +32128,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11">
       <c r="A333" s="10">
         <v>45417</v>
       </c>
@@ -32121,7 +32163,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11">
       <c r="A334" s="10">
         <v>45424</v>
       </c>
@@ -32156,7 +32198,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11">
       <c r="A335" s="10">
         <v>45431</v>
       </c>
@@ -32191,7 +32233,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11">
       <c r="A336" s="10">
         <v>45438</v>
       </c>
@@ -32226,7 +32268,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11">
       <c r="A337" s="10">
         <v>45445</v>
       </c>
@@ -32261,7 +32303,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11">
       <c r="A338" s="10">
         <v>45452</v>
       </c>
@@ -32296,7 +32338,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11">
       <c r="A339" s="10">
         <v>45459</v>
       </c>
@@ -32331,7 +32373,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11">
       <c r="A340" s="10">
         <v>45466</v>
       </c>
@@ -32366,7 +32408,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11">
       <c r="A341" s="10">
         <v>45473</v>
       </c>
@@ -32401,7 +32443,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11">
       <c r="A342" s="10">
         <v>45480</v>
       </c>
@@ -32436,7 +32478,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11">
       <c r="A343" s="10">
         <v>45487</v>
       </c>
@@ -32471,7 +32513,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11">
       <c r="A344" s="10">
         <v>45494</v>
       </c>
@@ -32506,7 +32548,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11">
       <c r="A345" s="10">
         <v>45501</v>
       </c>
@@ -32541,7 +32583,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11">
       <c r="A346" s="10">
         <v>45508</v>
       </c>
@@ -32576,7 +32618,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11">
       <c r="A347" s="10">
         <v>45515</v>
       </c>
@@ -32611,7 +32653,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11">
       <c r="A348" s="10">
         <v>45522</v>
       </c>
@@ -32646,7 +32688,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11">
       <c r="A349" s="10">
         <v>45529</v>
       </c>
@@ -32681,7 +32723,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11">
       <c r="A350" s="10">
         <v>45536</v>
       </c>
@@ -32716,7 +32758,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11">
       <c r="A351" s="10">
         <v>45543</v>
       </c>
@@ -32751,7 +32793,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11">
       <c r="A352" s="10">
         <v>45550</v>
       </c>
@@ -32786,7 +32828,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11">
       <c r="A353" s="10">
         <v>45557</v>
       </c>
@@ -32821,7 +32863,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11">
       <c r="A354" s="10">
         <v>45564</v>
       </c>
@@ -32856,7 +32898,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11">
       <c r="A355" s="10">
         <v>45571</v>
       </c>
@@ -32891,7 +32933,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11">
       <c r="A356" s="10">
         <v>45578</v>
       </c>
@@ -32926,7 +32968,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11">
       <c r="A357" s="10">
         <v>45585</v>
       </c>
@@ -32961,7 +33003,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11">
       <c r="A358" s="10">
         <v>45592</v>
       </c>
@@ -32996,7 +33038,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11">
       <c r="A359" s="10">
         <v>45599</v>
       </c>
@@ -33031,7 +33073,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11">
       <c r="A360" s="10">
         <v>45606</v>
       </c>
@@ -33066,7 +33108,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11">
       <c r="A361" s="10">
         <v>45613</v>
       </c>
@@ -33101,7 +33143,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11">
       <c r="A362" s="10">
         <v>45620</v>
       </c>
@@ -33136,7 +33178,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11">
       <c r="A363" s="10">
         <v>45627</v>
       </c>
@@ -33171,7 +33213,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11">
       <c r="A364" s="10">
         <v>45634</v>
       </c>
@@ -33206,7 +33248,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11">
       <c r="A365" s="10">
         <v>45641</v>
       </c>
@@ -33241,7 +33283,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11">
       <c r="A366" s="10">
         <v>45648</v>
       </c>
@@ -33276,7 +33318,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11">
       <c r="A367" s="10">
         <v>45655</v>
       </c>
@@ -33311,7 +33353,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11">
       <c r="A368" s="10">
         <v>45662</v>
       </c>
@@ -33346,7 +33388,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11">
       <c r="A369" s="10">
         <v>45669</v>
       </c>
@@ -33381,7 +33423,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11">
       <c r="A370" s="10">
         <v>45676</v>
       </c>
@@ -33416,7 +33458,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11">
       <c r="A371" s="10">
         <v>45683</v>
       </c>
@@ -33451,7 +33493,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11">
       <c r="A372" s="10">
         <v>45690</v>
       </c>
@@ -33486,7 +33528,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11">
       <c r="A373" s="10">
         <v>45697</v>
       </c>
@@ -33521,7 +33563,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11">
       <c r="A374" s="10">
         <v>45704</v>
       </c>
@@ -33556,7 +33598,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11">
       <c r="A375" s="10">
         <v>45711</v>
       </c>
@@ -33591,7 +33633,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11">
       <c r="A376" s="10">
         <v>45718</v>
       </c>
@@ -33626,7 +33668,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11">
       <c r="A377" s="10">
         <v>45725</v>
       </c>
@@ -33661,7 +33703,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11">
       <c r="A378" s="10">
         <v>45732</v>
       </c>
@@ -33696,7 +33738,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11">
       <c r="A379" s="10">
         <v>45739</v>
       </c>
@@ -33731,7 +33773,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11">
       <c r="A380" s="10">
         <v>45746</v>
       </c>
@@ -33766,7 +33808,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11">
       <c r="A381" s="10">
         <v>45753</v>
       </c>
@@ -33801,7 +33843,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11">
       <c r="A382" s="10">
         <v>45760</v>
       </c>
@@ -33836,7 +33878,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11">
       <c r="A383" s="10">
         <v>45767</v>
       </c>
@@ -33871,7 +33913,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11">
       <c r="A384" s="10">
         <v>45774</v>
       </c>
@@ -33906,7 +33948,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11">
       <c r="A385" s="10">
         <v>45781</v>
       </c>
@@ -33941,7 +33983,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11">
       <c r="A386" s="10">
         <v>45788</v>
       </c>
@@ -33976,7 +34018,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11">
       <c r="A387" s="10">
         <v>45795</v>
       </c>
@@ -34011,7 +34053,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11">
       <c r="A388" s="10">
         <v>45802</v>
       </c>
@@ -34046,7 +34088,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11">
       <c r="A389" s="10">
         <v>45809</v>
       </c>
@@ -34081,7 +34123,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11">
       <c r="A390" s="10">
         <v>45816</v>
       </c>
@@ -34116,7 +34158,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11">
       <c r="A391" s="10">
         <v>45823</v>
       </c>
@@ -34151,7 +34193,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11">
       <c r="A392" s="10">
         <v>45830</v>
       </c>
@@ -34186,7 +34228,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11">
       <c r="A393" s="10">
         <v>45837</v>
       </c>
@@ -34221,7 +34263,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11">
       <c r="A394" s="10">
         <v>45844</v>
       </c>
@@ -34256,7 +34298,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11">
       <c r="A395" s="10">
         <v>45851</v>
       </c>
@@ -34291,7 +34333,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11">
       <c r="A396" s="10">
         <v>45858</v>
       </c>
@@ -34326,7 +34368,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11">
       <c r="A397" s="10">
         <v>45865</v>
       </c>
@@ -34361,7 +34403,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11">
       <c r="A398" s="10">
         <v>45872</v>
       </c>
@@ -34396,7 +34438,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11">
       <c r="A399" s="10">
         <v>45879</v>
       </c>
@@ -34431,7 +34473,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11">
       <c r="A400" s="10">
         <v>45886</v>
       </c>
@@ -34466,7 +34508,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11">
       <c r="A401" s="10">
         <v>45893</v>
       </c>
@@ -34501,7 +34543,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11">
       <c r="A402" s="10">
         <v>45900</v>
       </c>
@@ -34536,7 +34578,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11">
       <c r="A403" s="10">
         <v>45907</v>
       </c>
@@ -34571,7 +34613,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11">
       <c r="A404" s="10">
         <v>45914</v>
       </c>
@@ -34606,7 +34648,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11">
       <c r="A405" s="10">
         <v>45921</v>
       </c>
@@ -34641,7 +34683,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11">
       <c r="A406" s="10">
         <v>45928</v>
       </c>
@@ -34676,7 +34718,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11">
       <c r="A407" s="10">
         <v>45935</v>
       </c>
@@ -34711,7 +34753,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11">
       <c r="A408" s="10">
         <v>45942</v>
       </c>
@@ -34746,7 +34788,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11">
       <c r="A409" s="10">
         <v>45949</v>
       </c>
@@ -34781,7 +34823,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11">
       <c r="A410" s="10">
         <v>45956</v>
       </c>
@@ -34816,7 +34858,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11">
       <c r="A411" s="10">
         <v>45963</v>
       </c>
@@ -34851,7 +34893,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11">
       <c r="A412" s="10">
         <v>45970</v>
       </c>
@@ -34886,7 +34928,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11">
       <c r="A413" s="10">
         <v>45977</v>
       </c>
@@ -34921,7 +34963,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11">
       <c r="A414" s="10">
         <v>45984</v>
       </c>
@@ -34956,7 +34998,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11">
       <c r="A415" s="10">
         <v>45991</v>
       </c>
@@ -34991,7 +35033,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11">
       <c r="A416" s="10">
         <v>45998</v>
       </c>
@@ -35026,7 +35068,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11">
       <c r="A417" s="10">
         <v>46005</v>
       </c>
@@ -35061,7 +35103,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11">
       <c r="A418" s="10">
         <v>46012</v>
       </c>
@@ -35096,7 +35138,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11">
       <c r="A419" s="10">
         <v>46026</v>
       </c>
@@ -35131,7 +35173,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11">
       <c r="A420" s="10">
         <v>46033</v>
       </c>
@@ -35166,7 +35208,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11">
       <c r="A421" s="10">
         <v>46040</v>
       </c>
@@ -35201,7 +35243,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11">
       <c r="A422" s="10">
         <v>46047</v>
       </c>
@@ -35236,7 +35278,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11">
       <c r="A423" s="10">
         <v>46054</v>
       </c>
@@ -35271,7 +35313,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11">
       <c r="A424" s="10">
         <v>46061</v>
       </c>
@@ -35306,7 +35348,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11">
       <c r="A425" s="10">
         <v>46068</v>
       </c>
@@ -35341,7 +35383,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11">
       <c r="A426" s="10">
         <v>46075</v>
       </c>
@@ -35376,7 +35418,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11">
       <c r="A427" s="10">
         <v>46082</v>
       </c>
@@ -35411,7 +35453,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11">
       <c r="A428" s="10">
         <v>46089</v>
       </c>
@@ -35446,7 +35488,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11">
       <c r="A429" s="10">
         <v>46096</v>
       </c>
@@ -35481,7 +35523,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11">
       <c r="A430" s="10">
         <v>46103</v>
       </c>
@@ -35516,7 +35558,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11">
       <c r="A431" s="10">
         <v>46110</v>
       </c>
@@ -35551,7 +35593,7 @@
         <v>5348</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11">
       <c r="A432" s="10">
         <v>46117</v>
       </c>
@@ -35586,7 +35628,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11">
       <c r="A433" s="10">
         <v>46124</v>
       </c>
@@ -35621,7 +35663,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11">
       <c r="A434" s="10">
         <v>46131</v>
       </c>
@@ -35656,7 +35698,7 @@
         <v>5837</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11">
       <c r="A435" s="10">
         <v>46138</v>
       </c>
@@ -35691,7 +35733,7 @@
         <v>5881</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11">
       <c r="A436" s="10">
         <v>46145</v>
       </c>
@@ -35726,7 +35768,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11">
       <c r="A437" s="10">
         <v>46152</v>
       </c>
@@ -35761,7 +35803,7 @@
         <v>5909</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11">
       <c r="A438" s="10">
         <v>46159</v>
       </c>
@@ -35796,7 +35838,7 @@
         <v>5807</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11">
       <c r="A439" s="10">
         <v>46166</v>
       </c>
@@ -35831,7 +35873,7 @@
         <v>5932</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11">
       <c r="A440" s="10">
         <v>46173</v>
       </c>
@@ -35866,7 +35908,7 @@
         <v>5984</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11">
       <c r="A441" s="10">
         <v>46180</v>
       </c>
@@ -35901,7 +35943,7 @@
         <v>6121</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11">
       <c r="A442" s="10">
         <v>46187</v>
       </c>
@@ -35936,7 +35978,7 @@
         <v>6025</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11">
       <c r="A443" s="10">
         <v>46194</v>
       </c>
@@ -35971,7 +36013,7 @@
         <v>6239</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11">
       <c r="A444" s="10">
         <v>46201</v>
       </c>
@@ -36006,7 +36048,7 @@
         <v>5992</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11">
       <c r="A445" s="10">
         <v>46208</v>
       </c>
@@ -36039,6 +36081,41 @@
       </c>
       <c r="K445" s="13">
         <v>5634</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11">
+      <c r="A446" s="10">
+        <v>46215</v>
+      </c>
+      <c r="B446" s="11">
+        <v>46216</v>
+      </c>
+      <c r="C446" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D446" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E446" s="13">
+        <v>2486</v>
+      </c>
+      <c r="F446" s="13">
+        <v>1165</v>
+      </c>
+      <c r="G446" s="13">
+        <v>4280</v>
+      </c>
+      <c r="H446" s="13">
+        <v>1164</v>
+      </c>
+      <c r="I446" s="13">
+        <v>1134</v>
+      </c>
+      <c r="J446" s="13">
+        <v>311</v>
+      </c>
+      <c r="K446" s="13">
+        <v>5533</v>
       </c>
     </row>
   </sheetData>
@@ -36052,7 +36129,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
@@ -36068,12 +36145,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" ht="16">
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
@@ -36085,7 +36162,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C22B23-1403-4FCB-8AF3-A4DC23B1C67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5F5898-C548-4944-945E-5EDED2F0A3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -109,29 +109,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -153,7 +153,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -170,7 +170,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -214,7 +214,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -235,33 +235,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -279,7 +279,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1663,6 +1663,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3006,6 +3009,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>2486</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>2408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4384,6 +4390,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5727,6 +5736,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>1165</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7105,6 +7117,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8448,6 +8463,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>4280</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9826,6 +9844,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11169,6 +11190,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>1164</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12547,6 +12571,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13890,6 +13917,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>1134</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15270,6 +15300,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16613,6 +16646,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>5533</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>5473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18007,6 +18043,9 @@
                 <c:pt idx="444">
                   <c:v>46216</c:v>
                 </c:pt>
+                <c:pt idx="445">
+                  <c:v>46223</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19350,6 +19389,9 @@
                 </c:pt>
                 <c:pt idx="444">
                   <c:v>311</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20496,19 +20538,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K446"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:K447"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="7.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="7.19921875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.796875" style="13" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
@@ -20543,7 +20585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>43100</v>
       </c>
@@ -20578,7 +20620,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>43107</v>
       </c>
@@ -20613,7 +20655,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>43114</v>
       </c>
@@ -20648,7 +20690,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>43121</v>
       </c>
@@ -20683,7 +20725,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>43128</v>
       </c>
@@ -20718,7 +20760,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>43135</v>
       </c>
@@ -20753,7 +20795,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>43142</v>
       </c>
@@ -20788,7 +20830,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>43149</v>
       </c>
@@ -20823,7 +20865,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>43156</v>
       </c>
@@ -20858,7 +20900,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>43163</v>
       </c>
@@ -20893,7 +20935,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>43170</v>
       </c>
@@ -20928,7 +20970,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>43177</v>
       </c>
@@ -20963,7 +21005,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>43184</v>
       </c>
@@ -20998,7 +21040,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>43191</v>
       </c>
@@ -21033,7 +21075,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>43198</v>
       </c>
@@ -21068,7 +21110,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>43205</v>
       </c>
@@ -21103,7 +21145,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>43212</v>
       </c>
@@ -21138,7 +21180,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>43219</v>
       </c>
@@ -21173,7 +21215,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>43226</v>
       </c>
@@ -21208,7 +21250,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>43233</v>
       </c>
@@ -21243,7 +21285,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>43240</v>
       </c>
@@ -21278,7 +21320,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>43247</v>
       </c>
@@ -21313,7 +21355,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>43254</v>
       </c>
@@ -21348,7 +21390,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>43261</v>
       </c>
@@ -21383,7 +21425,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>43268</v>
       </c>
@@ -21418,7 +21460,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>43275</v>
       </c>
@@ -21453,7 +21495,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>43282</v>
       </c>
@@ -21488,7 +21530,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>43289</v>
       </c>
@@ -21523,7 +21565,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>43296</v>
       </c>
@@ -21558,7 +21600,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>43303</v>
       </c>
@@ -21593,7 +21635,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>43310</v>
       </c>
@@ -21628,7 +21670,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>43317</v>
       </c>
@@ -21663,7 +21705,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>43324</v>
       </c>
@@ -21698,7 +21740,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>43331</v>
       </c>
@@ -21733,7 +21775,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>43338</v>
       </c>
@@ -21768,7 +21810,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>43345</v>
       </c>
@@ -21803,7 +21845,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>43352</v>
       </c>
@@ -21838,7 +21880,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>43359</v>
       </c>
@@ -21873,7 +21915,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>43366</v>
       </c>
@@ -21908,7 +21950,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>43373</v>
       </c>
@@ -21943,7 +21985,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>43380</v>
       </c>
@@ -21978,7 +22020,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>43387</v>
       </c>
@@ -22013,7 +22055,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>43394</v>
       </c>
@@ -22048,7 +22090,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>43401</v>
       </c>
@@ -22083,7 +22125,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>43408</v>
       </c>
@@ -22118,7 +22160,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>43415</v>
       </c>
@@ -22153,7 +22195,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>43422</v>
       </c>
@@ -22188,7 +22230,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>43429</v>
       </c>
@@ -22223,7 +22265,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>43436</v>
       </c>
@@ -22258,7 +22300,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>43443</v>
       </c>
@@ -22293,7 +22335,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>43450</v>
       </c>
@@ -22328,7 +22370,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>43457</v>
       </c>
@@ -22363,7 +22405,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43464</v>
       </c>
@@ -22398,7 +22440,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>43471</v>
       </c>
@@ -22433,7 +22475,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43478</v>
       </c>
@@ -22468,7 +22510,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>43485</v>
       </c>
@@ -22503,7 +22545,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43492</v>
       </c>
@@ -22538,7 +22580,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>43499</v>
       </c>
@@ -22573,7 +22615,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43506</v>
       </c>
@@ -22608,7 +22650,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>43513</v>
       </c>
@@ -22643,7 +22685,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43520</v>
       </c>
@@ -22678,7 +22720,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>43527</v>
       </c>
@@ -22713,7 +22755,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43534</v>
       </c>
@@ -22748,7 +22790,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>43541</v>
       </c>
@@ -22783,7 +22825,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43548</v>
       </c>
@@ -22818,7 +22860,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>43555</v>
       </c>
@@ -22853,7 +22895,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43562</v>
       </c>
@@ -22888,7 +22930,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>43569</v>
       </c>
@@ -22923,7 +22965,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43576</v>
       </c>
@@ -22958,7 +23000,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>43583</v>
       </c>
@@ -22993,7 +23035,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43590</v>
       </c>
@@ -23028,7 +23070,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>43597</v>
       </c>
@@ -23063,7 +23105,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43604</v>
       </c>
@@ -23098,7 +23140,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>43611</v>
       </c>
@@ -23133,7 +23175,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43618</v>
       </c>
@@ -23168,7 +23210,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>43625</v>
       </c>
@@ -23203,7 +23245,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43632</v>
       </c>
@@ -23238,7 +23280,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>43639</v>
       </c>
@@ -23273,7 +23315,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43646</v>
       </c>
@@ -23308,7 +23350,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="10">
         <v>43653</v>
       </c>
@@ -23343,7 +23385,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43660</v>
       </c>
@@ -23378,7 +23420,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="10">
         <v>43667</v>
       </c>
@@ -23413,7 +23455,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43674</v>
       </c>
@@ -23448,7 +23490,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>43681</v>
       </c>
@@ -23483,7 +23525,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>43688</v>
       </c>
@@ -23518,7 +23560,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>43695</v>
       </c>
@@ -23553,7 +23595,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>43702</v>
       </c>
@@ -23588,7 +23630,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="10">
         <v>43709</v>
       </c>
@@ -23623,7 +23665,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>43716</v>
       </c>
@@ -23658,7 +23700,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <v>43723</v>
       </c>
@@ -23693,7 +23735,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>43730</v>
       </c>
@@ -23728,7 +23770,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <v>43737</v>
       </c>
@@ -23763,7 +23805,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>43744</v>
       </c>
@@ -23798,7 +23840,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <v>43751</v>
       </c>
@@ -23833,7 +23875,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>43758</v>
       </c>
@@ -23868,7 +23910,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>43765</v>
       </c>
@@ -23903,7 +23945,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>43772</v>
       </c>
@@ -23938,7 +23980,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>43779</v>
       </c>
@@ -23973,7 +24015,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>43786</v>
       </c>
@@ -24008,7 +24050,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>43793</v>
       </c>
@@ -24043,7 +24085,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>43800</v>
       </c>
@@ -24078,7 +24120,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>43807</v>
       </c>
@@ -24113,7 +24155,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>43814</v>
       </c>
@@ -24148,7 +24190,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>43821</v>
       </c>
@@ -24183,7 +24225,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>43828</v>
       </c>
@@ -24218,7 +24260,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>43835</v>
       </c>
@@ -24253,7 +24295,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>43842</v>
       </c>
@@ -24288,7 +24330,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>43849</v>
       </c>
@@ -24323,7 +24365,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>43856</v>
       </c>
@@ -24358,7 +24400,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>43863</v>
       </c>
@@ -24393,7 +24435,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>43870</v>
       </c>
@@ -24428,7 +24470,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>43877</v>
       </c>
@@ -24463,7 +24505,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>43884</v>
       </c>
@@ -24498,7 +24540,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>43891</v>
       </c>
@@ -24533,7 +24575,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>43898</v>
       </c>
@@ -24568,7 +24610,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>43905</v>
       </c>
@@ -24603,7 +24645,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>43912</v>
       </c>
@@ -24638,7 +24680,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>43919</v>
       </c>
@@ -24673,7 +24715,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>43926</v>
       </c>
@@ -24708,7 +24750,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="10">
         <v>43933</v>
       </c>
@@ -24743,7 +24785,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>43940</v>
       </c>
@@ -24778,7 +24820,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="10">
         <v>43947</v>
       </c>
@@ -24813,7 +24855,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>43954</v>
       </c>
@@ -24848,7 +24890,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>43961</v>
       </c>
@@ -24883,7 +24925,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>43968</v>
       </c>
@@ -24918,7 +24960,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="10">
         <v>43975</v>
       </c>
@@ -24953,7 +24995,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>43982</v>
       </c>
@@ -24988,7 +25030,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>43989</v>
       </c>
@@ -25023,7 +25065,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>43996</v>
       </c>
@@ -25058,7 +25100,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>44003</v>
       </c>
@@ -25093,7 +25135,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>44010</v>
       </c>
@@ -25128,7 +25170,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>44017</v>
       </c>
@@ -25163,7 +25205,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>44024</v>
       </c>
@@ -25198,7 +25240,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44031</v>
       </c>
@@ -25233,7 +25275,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>44038</v>
       </c>
@@ -25268,7 +25310,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44045</v>
       </c>
@@ -25303,7 +25345,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>44052</v>
       </c>
@@ -25338,7 +25380,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44059</v>
       </c>
@@ -25373,7 +25415,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>44066</v>
       </c>
@@ -25408,7 +25450,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44073</v>
       </c>
@@ -25443,7 +25485,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>44080</v>
       </c>
@@ -25478,7 +25520,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>44087</v>
       </c>
@@ -25513,7 +25555,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>44094</v>
       </c>
@@ -25548,7 +25590,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>44101</v>
       </c>
@@ -25583,7 +25625,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>44108</v>
       </c>
@@ -25618,7 +25660,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>44115</v>
       </c>
@@ -25653,7 +25695,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>44122</v>
       </c>
@@ -25688,7 +25730,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44129</v>
       </c>
@@ -25723,7 +25765,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>44136</v>
       </c>
@@ -25758,7 +25800,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>44143</v>
       </c>
@@ -25793,7 +25835,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>44150</v>
       </c>
@@ -25828,7 +25870,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>44157</v>
       </c>
@@ -25863,7 +25905,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>44164</v>
       </c>
@@ -25898,7 +25940,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>44171</v>
       </c>
@@ -25933,7 +25975,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>44178</v>
       </c>
@@ -25968,7 +26010,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>44185</v>
       </c>
@@ -26003,7 +26045,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>44192</v>
       </c>
@@ -26038,7 +26080,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>44199</v>
       </c>
@@ -26073,7 +26115,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44206</v>
       </c>
@@ -26108,7 +26150,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>44213</v>
       </c>
@@ -26143,7 +26185,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44220</v>
       </c>
@@ -26178,7 +26220,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>44227</v>
       </c>
@@ -26213,7 +26255,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>44234</v>
       </c>
@@ -26248,7 +26290,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>44241</v>
       </c>
@@ -26283,7 +26325,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>44248</v>
       </c>
@@ -26318,7 +26360,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>44255</v>
       </c>
@@ -26353,7 +26395,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>44262</v>
       </c>
@@ -26388,7 +26430,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>44269</v>
       </c>
@@ -26423,7 +26465,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>44276</v>
       </c>
@@ -26458,7 +26500,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>44283</v>
       </c>
@@ -26493,7 +26535,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>44290</v>
       </c>
@@ -26528,7 +26570,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>44297</v>
       </c>
@@ -26563,7 +26605,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>44304</v>
       </c>
@@ -26598,7 +26640,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>44311</v>
       </c>
@@ -26633,7 +26675,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>44318</v>
       </c>
@@ -26668,7 +26710,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>44325</v>
       </c>
@@ -26703,7 +26745,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>44332</v>
       </c>
@@ -26738,7 +26780,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>44339</v>
       </c>
@@ -26773,7 +26815,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>44346</v>
       </c>
@@ -26808,7 +26850,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>44353</v>
       </c>
@@ -26843,7 +26885,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="10">
         <v>44360</v>
       </c>
@@ -26878,7 +26920,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>44367</v>
       </c>
@@ -26913,7 +26955,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>44374</v>
       </c>
@@ -26948,7 +26990,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>44381</v>
       </c>
@@ -26983,7 +27025,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>44388</v>
       </c>
@@ -27018,7 +27060,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>44395</v>
       </c>
@@ -27053,7 +27095,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>44402</v>
       </c>
@@ -27088,7 +27130,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>44409</v>
       </c>
@@ -27123,7 +27165,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>44416</v>
       </c>
@@ -27158,7 +27200,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="10">
         <v>44423</v>
       </c>
@@ -27193,7 +27235,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>44430</v>
       </c>
@@ -27228,7 +27270,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="10">
         <v>44437</v>
       </c>
@@ -27263,7 +27305,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>44444</v>
       </c>
@@ -27298,7 +27340,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="10">
         <v>44451</v>
       </c>
@@ -27333,7 +27375,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>44458</v>
       </c>
@@ -27368,7 +27410,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="10">
         <v>44465</v>
       </c>
@@ -27403,7 +27445,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>44472</v>
       </c>
@@ -27438,7 +27480,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="10">
         <v>44479</v>
       </c>
@@ -27473,7 +27515,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>44486</v>
       </c>
@@ -27508,7 +27550,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="10">
         <v>44493</v>
       </c>
@@ -27543,7 +27585,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>44500</v>
       </c>
@@ -27578,7 +27620,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <v>44507</v>
       </c>
@@ -27613,7 +27655,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>44514</v>
       </c>
@@ -27648,7 +27690,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <v>44521</v>
       </c>
@@ -27683,7 +27725,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>44528</v>
       </c>
@@ -27718,7 +27760,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <v>44535</v>
       </c>
@@ -27753,7 +27795,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>44542</v>
       </c>
@@ -27788,7 +27830,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>44549</v>
       </c>
@@ -27823,7 +27865,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="10">
         <v>44556</v>
       </c>
@@ -27858,7 +27900,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>44563</v>
       </c>
@@ -27893,7 +27935,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="10">
         <v>44570</v>
       </c>
@@ -27928,7 +27970,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>44577</v>
       </c>
@@ -27963,7 +28005,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="10">
         <v>44584</v>
       </c>
@@ -27998,7 +28040,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>44591</v>
       </c>
@@ -28033,7 +28075,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="10">
         <v>44598</v>
       </c>
@@ -28068,7 +28110,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>44605</v>
       </c>
@@ -28103,7 +28145,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="10">
         <v>44612</v>
       </c>
@@ -28138,7 +28180,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>44619</v>
       </c>
@@ -28173,7 +28215,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="10">
         <v>44626</v>
       </c>
@@ -28208,7 +28250,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>44633</v>
       </c>
@@ -28243,7 +28285,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>44640</v>
       </c>
@@ -28278,7 +28320,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>44647</v>
       </c>
@@ -28313,7 +28355,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>44654</v>
       </c>
@@ -28348,7 +28390,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>44661</v>
       </c>
@@ -28383,7 +28425,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>44668</v>
       </c>
@@ -28418,7 +28460,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>44675</v>
       </c>
@@ -28453,7 +28495,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>44682</v>
       </c>
@@ -28488,7 +28530,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="10">
         <v>44689</v>
       </c>
@@ -28523,7 +28565,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>44696</v>
       </c>
@@ -28558,7 +28600,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" s="10">
         <v>44703</v>
       </c>
@@ -28593,7 +28635,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>44710</v>
       </c>
@@ -28628,7 +28670,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" s="10">
         <v>44717</v>
       </c>
@@ -28663,7 +28705,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>44724</v>
       </c>
@@ -28698,7 +28740,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" s="10">
         <v>44731</v>
       </c>
@@ -28733,7 +28775,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>44738</v>
       </c>
@@ -28768,7 +28810,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" s="10">
         <v>44745</v>
       </c>
@@ -28803,7 +28845,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>44752</v>
       </c>
@@ -28838,7 +28880,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" s="10">
         <v>44759</v>
       </c>
@@ -28873,7 +28915,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>44766</v>
       </c>
@@ -28908,7 +28950,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="10">
         <v>44773</v>
       </c>
@@ -28943,7 +28985,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="10">
         <v>44780</v>
       </c>
@@ -28978,7 +29020,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="10">
         <v>44787</v>
       </c>
@@ -29013,7 +29055,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>44794</v>
       </c>
@@ -29048,7 +29090,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" s="10">
         <v>44801</v>
       </c>
@@ -29083,7 +29125,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="10">
         <v>44808</v>
       </c>
@@ -29118,7 +29160,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>44815</v>
       </c>
@@ -29153,7 +29195,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="10">
         <v>44822</v>
       </c>
@@ -29188,7 +29230,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>44829</v>
       </c>
@@ -29223,7 +29265,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="10">
         <v>44836</v>
       </c>
@@ -29258,7 +29300,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>44843</v>
       </c>
@@ -29293,7 +29335,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" s="10">
         <v>44850</v>
       </c>
@@ -29328,7 +29370,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>44857</v>
       </c>
@@ -29363,7 +29405,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="10">
         <v>44864</v>
       </c>
@@ -29398,7 +29440,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>44871</v>
       </c>
@@ -29433,7 +29475,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="10">
         <v>44878</v>
       </c>
@@ -29468,7 +29510,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>44885</v>
       </c>
@@ -29503,7 +29545,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" s="10">
         <v>44892</v>
       </c>
@@ -29538,7 +29580,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>44899</v>
       </c>
@@ -29573,7 +29615,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="10">
         <v>44906</v>
       </c>
@@ -29608,7 +29650,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="10">
         <v>44913</v>
       </c>
@@ -29643,7 +29685,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="10">
         <v>44920</v>
       </c>
@@ -29678,7 +29720,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="10">
         <v>44927</v>
       </c>
@@ -29713,7 +29755,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="10">
         <v>44934</v>
       </c>
@@ -29748,7 +29790,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" s="10">
         <v>44941</v>
       </c>
@@ -29783,7 +29825,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="10">
         <v>44948</v>
       </c>
@@ -29818,7 +29860,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="10">
         <v>44955</v>
       </c>
@@ -29853,7 +29895,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>44962</v>
       </c>
@@ -29888,7 +29930,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="10">
         <v>44969</v>
       </c>
@@ -29923,7 +29965,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="10">
         <v>44976</v>
       </c>
@@ -29958,7 +30000,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="10">
         <v>44983</v>
       </c>
@@ -29993,7 +30035,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="10">
         <v>44990</v>
       </c>
@@ -30028,7 +30070,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="10">
         <v>44997</v>
       </c>
@@ -30063,7 +30105,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="10">
         <v>45004</v>
       </c>
@@ -30098,7 +30140,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="10">
         <v>45011</v>
       </c>
@@ -30133,7 +30175,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="10">
         <v>45018</v>
       </c>
@@ -30168,7 +30210,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="10">
         <v>45025</v>
       </c>
@@ -30203,7 +30245,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="10">
         <v>45032</v>
       </c>
@@ -30238,7 +30280,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="10">
         <v>45039</v>
       </c>
@@ -30273,7 +30315,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="10">
         <v>45046</v>
       </c>
@@ -30308,7 +30350,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="10">
         <v>45053</v>
       </c>
@@ -30343,7 +30385,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="10">
         <v>45060</v>
       </c>
@@ -30378,7 +30420,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="10">
         <v>45067</v>
       </c>
@@ -30413,7 +30455,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="10">
         <v>45074</v>
       </c>
@@ -30448,7 +30490,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="10">
         <v>45081</v>
       </c>
@@ -30483,7 +30525,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="10">
         <v>45088</v>
       </c>
@@ -30518,7 +30560,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="10">
         <v>45095</v>
       </c>
@@ -30553,7 +30595,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="10">
         <v>45102</v>
       </c>
@@ -30588,7 +30630,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="10">
         <v>45109</v>
       </c>
@@ -30623,7 +30665,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="10">
         <v>45116</v>
       </c>
@@ -30658,7 +30700,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="10">
         <v>45123</v>
       </c>
@@ -30693,7 +30735,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="10">
         <v>45130</v>
       </c>
@@ -30728,7 +30770,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="10">
         <v>45137</v>
       </c>
@@ -30763,7 +30805,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="10">
         <v>45144</v>
       </c>
@@ -30798,7 +30840,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="10">
         <v>45151</v>
       </c>
@@ -30833,7 +30875,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="10">
         <v>45158</v>
       </c>
@@ -30868,7 +30910,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="10">
         <v>45165</v>
       </c>
@@ -30903,7 +30945,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="10">
         <v>45172</v>
       </c>
@@ -30938,7 +30980,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="10">
         <v>45179</v>
       </c>
@@ -30973,7 +31015,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="10">
         <v>45186</v>
       </c>
@@ -31008,7 +31050,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="10">
         <v>45193</v>
       </c>
@@ -31043,7 +31085,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="10">
         <v>45200</v>
       </c>
@@ -31078,7 +31120,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="10">
         <v>45207</v>
       </c>
@@ -31113,7 +31155,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="10">
         <v>45214</v>
       </c>
@@ -31148,7 +31190,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="10">
         <v>45221</v>
       </c>
@@ -31183,7 +31225,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="10">
         <v>45228</v>
       </c>
@@ -31218,7 +31260,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="10">
         <v>45235</v>
       </c>
@@ -31253,7 +31295,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="10">
         <v>45242</v>
       </c>
@@ -31288,7 +31330,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="10">
         <v>45249</v>
       </c>
@@ -31323,7 +31365,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="10">
         <v>45256</v>
       </c>
@@ -31358,7 +31400,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="10">
         <v>45263</v>
       </c>
@@ -31393,7 +31435,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="10">
         <v>45270</v>
       </c>
@@ -31428,7 +31470,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="10">
         <v>45277</v>
       </c>
@@ -31463,7 +31505,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="10">
         <v>45284</v>
       </c>
@@ -31498,7 +31540,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" s="10">
         <v>45291</v>
       </c>
@@ -31533,7 +31575,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="10">
         <v>45298</v>
       </c>
@@ -31568,7 +31610,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="10">
         <v>45305</v>
       </c>
@@ -31603,7 +31645,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="10">
         <v>45312</v>
       </c>
@@ -31638,7 +31680,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="10">
         <v>45319</v>
       </c>
@@ -31673,7 +31715,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" s="10">
         <v>45326</v>
       </c>
@@ -31708,7 +31750,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="10">
         <v>45333</v>
       </c>
@@ -31743,7 +31785,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="10">
         <v>45340</v>
       </c>
@@ -31778,7 +31820,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="10">
         <v>45347</v>
       </c>
@@ -31813,7 +31855,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="10">
         <v>45354</v>
       </c>
@@ -31848,7 +31890,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="10">
         <v>45361</v>
       </c>
@@ -31883,7 +31925,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="10">
         <v>45368</v>
       </c>
@@ -31918,7 +31960,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" s="10">
         <v>45375</v>
       </c>
@@ -31953,7 +31995,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="10">
         <v>45382</v>
       </c>
@@ -31988,7 +32030,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="10">
         <v>45389</v>
       </c>
@@ -32023,7 +32065,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="10">
         <v>45396</v>
       </c>
@@ -32058,7 +32100,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="10">
         <v>45403</v>
       </c>
@@ -32093,7 +32135,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="10">
         <v>45410</v>
       </c>
@@ -32128,7 +32170,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" s="10">
         <v>45417</v>
       </c>
@@ -32163,7 +32205,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" s="10">
         <v>45424</v>
       </c>
@@ -32198,7 +32240,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" s="10">
         <v>45431</v>
       </c>
@@ -32233,7 +32275,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" s="10">
         <v>45438</v>
       </c>
@@ -32268,7 +32310,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" s="10">
         <v>45445</v>
       </c>
@@ -32303,7 +32345,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="10">
         <v>45452</v>
       </c>
@@ -32338,7 +32380,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="10">
         <v>45459</v>
       </c>
@@ -32373,7 +32415,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="10">
         <v>45466</v>
       </c>
@@ -32408,7 +32450,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="10">
         <v>45473</v>
       </c>
@@ -32443,7 +32485,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="10">
         <v>45480</v>
       </c>
@@ -32478,7 +32520,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="10">
         <v>45487</v>
       </c>
@@ -32513,7 +32555,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="10">
         <v>45494</v>
       </c>
@@ -32548,7 +32590,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="10">
         <v>45501</v>
       </c>
@@ -32583,7 +32625,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="10">
         <v>45508</v>
       </c>
@@ -32618,7 +32660,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="10">
         <v>45515</v>
       </c>
@@ -32653,7 +32695,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="10">
         <v>45522</v>
       </c>
@@ -32688,7 +32730,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="10">
         <v>45529</v>
       </c>
@@ -32723,7 +32765,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="10">
         <v>45536</v>
       </c>
@@ -32758,7 +32800,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="10">
         <v>45543</v>
       </c>
@@ -32793,7 +32835,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="10">
         <v>45550</v>
       </c>
@@ -32828,7 +32870,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="10">
         <v>45557</v>
       </c>
@@ -32863,7 +32905,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="10">
         <v>45564</v>
       </c>
@@ -32898,7 +32940,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="10">
         <v>45571</v>
       </c>
@@ -32933,7 +32975,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="10">
         <v>45578</v>
       </c>
@@ -32968,7 +33010,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="10">
         <v>45585</v>
       </c>
@@ -33003,7 +33045,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="10">
         <v>45592</v>
       </c>
@@ -33038,7 +33080,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="10">
         <v>45599</v>
       </c>
@@ -33073,7 +33115,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="10">
         <v>45606</v>
       </c>
@@ -33108,7 +33150,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="10">
         <v>45613</v>
       </c>
@@ -33143,7 +33185,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="10">
         <v>45620</v>
       </c>
@@ -33178,7 +33220,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="10">
         <v>45627</v>
       </c>
@@ -33213,7 +33255,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="10">
         <v>45634</v>
       </c>
@@ -33248,7 +33290,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="10">
         <v>45641</v>
       </c>
@@ -33283,7 +33325,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" s="10">
         <v>45648</v>
       </c>
@@ -33318,7 +33360,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" s="10">
         <v>45655</v>
       </c>
@@ -33353,7 +33395,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" s="10">
         <v>45662</v>
       </c>
@@ -33388,7 +33430,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="10">
         <v>45669</v>
       </c>
@@ -33423,7 +33465,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="10">
         <v>45676</v>
       </c>
@@ -33458,7 +33500,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="10">
         <v>45683</v>
       </c>
@@ -33493,7 +33535,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="10">
         <v>45690</v>
       </c>
@@ -33528,7 +33570,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="10">
         <v>45697</v>
       </c>
@@ -33563,7 +33605,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="10">
         <v>45704</v>
       </c>
@@ -33598,7 +33640,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="10">
         <v>45711</v>
       </c>
@@ -33633,7 +33675,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="10">
         <v>45718</v>
       </c>
@@ -33668,7 +33710,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="10">
         <v>45725</v>
       </c>
@@ -33703,7 +33745,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="10">
         <v>45732</v>
       </c>
@@ -33738,7 +33780,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="10">
         <v>45739</v>
       </c>
@@ -33773,7 +33815,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="10">
         <v>45746</v>
       </c>
@@ -33808,7 +33850,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="10">
         <v>45753</v>
       </c>
@@ -33843,7 +33885,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="10">
         <v>45760</v>
       </c>
@@ -33878,7 +33920,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="10">
         <v>45767</v>
       </c>
@@ -33913,7 +33955,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="10">
         <v>45774</v>
       </c>
@@ -33948,7 +33990,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" s="10">
         <v>45781</v>
       </c>
@@ -33983,7 +34025,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" s="10">
         <v>45788</v>
       </c>
@@ -34018,7 +34060,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" s="10">
         <v>45795</v>
       </c>
@@ -34053,7 +34095,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="10">
         <v>45802</v>
       </c>
@@ -34088,7 +34130,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" s="10">
         <v>45809</v>
       </c>
@@ -34123,7 +34165,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" s="10">
         <v>45816</v>
       </c>
@@ -34158,7 +34200,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="10">
         <v>45823</v>
       </c>
@@ -34193,7 +34235,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="10">
         <v>45830</v>
       </c>
@@ -34228,7 +34270,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="10">
         <v>45837</v>
       </c>
@@ -34263,7 +34305,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="10">
         <v>45844</v>
       </c>
@@ -34298,7 +34340,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="10">
         <v>45851</v>
       </c>
@@ -34333,7 +34375,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="10">
         <v>45858</v>
       </c>
@@ -34368,7 +34410,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="10">
         <v>45865</v>
       </c>
@@ -34403,7 +34445,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="10">
         <v>45872</v>
       </c>
@@ -34438,7 +34480,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="10">
         <v>45879</v>
       </c>
@@ -34473,7 +34515,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="10">
         <v>45886</v>
       </c>
@@ -34508,7 +34550,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="10">
         <v>45893</v>
       </c>
@@ -34543,7 +34585,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="10">
         <v>45900</v>
       </c>
@@ -34578,7 +34620,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="10">
         <v>45907</v>
       </c>
@@ -34613,7 +34655,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="10">
         <v>45914</v>
       </c>
@@ -34648,7 +34690,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="10">
         <v>45921</v>
       </c>
@@ -34683,7 +34725,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="10">
         <v>45928</v>
       </c>
@@ -34718,7 +34760,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="10">
         <v>45935</v>
       </c>
@@ -34753,7 +34795,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="10">
         <v>45942</v>
       </c>
@@ -34788,7 +34830,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="10">
         <v>45949</v>
       </c>
@@ -34823,7 +34865,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="10">
         <v>45956</v>
       </c>
@@ -34858,7 +34900,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="10">
         <v>45963</v>
       </c>
@@ -34893,7 +34935,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="10">
         <v>45970</v>
       </c>
@@ -34928,7 +34970,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="10">
         <v>45977</v>
       </c>
@@ -34963,7 +35005,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="10">
         <v>45984</v>
       </c>
@@ -34998,7 +35040,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="10">
         <v>45991</v>
       </c>
@@ -35033,7 +35075,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="10">
         <v>45998</v>
       </c>
@@ -35068,7 +35110,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="10">
         <v>46005</v>
       </c>
@@ -35103,7 +35145,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="10">
         <v>46012</v>
       </c>
@@ -35138,7 +35180,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="10">
         <v>46026</v>
       </c>
@@ -35173,7 +35215,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="10">
         <v>46033</v>
       </c>
@@ -35208,7 +35250,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="10">
         <v>46040</v>
       </c>
@@ -35243,7 +35285,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="10">
         <v>46047</v>
       </c>
@@ -35278,7 +35320,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="10">
         <v>46054</v>
       </c>
@@ -35313,7 +35355,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="10">
         <v>46061</v>
       </c>
@@ -35348,7 +35390,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="10">
         <v>46068</v>
       </c>
@@ -35383,7 +35425,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="10">
         <v>46075</v>
       </c>
@@ -35418,7 +35460,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="10">
         <v>46082</v>
       </c>
@@ -35453,7 +35495,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="10">
         <v>46089</v>
       </c>
@@ -35488,7 +35530,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="10">
         <v>46096</v>
       </c>
@@ -35523,7 +35565,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="10">
         <v>46103</v>
       </c>
@@ -35558,7 +35600,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" s="10">
         <v>46110</v>
       </c>
@@ -35593,7 +35635,7 @@
         <v>5348</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="10">
         <v>46117</v>
       </c>
@@ -35628,7 +35670,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="10">
         <v>46124</v>
       </c>
@@ -35663,7 +35705,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="10">
         <v>46131</v>
       </c>
@@ -35698,7 +35740,7 @@
         <v>5837</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="10">
         <v>46138</v>
       </c>
@@ -35733,7 +35775,7 @@
         <v>5881</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="10">
         <v>46145</v>
       </c>
@@ -35768,7 +35810,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="10">
         <v>46152</v>
       </c>
@@ -35803,7 +35845,7 @@
         <v>5909</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="10">
         <v>46159</v>
       </c>
@@ -35838,7 +35880,7 @@
         <v>5807</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="10">
         <v>46166</v>
       </c>
@@ -35873,7 +35915,7 @@
         <v>5932</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" s="10">
         <v>46173</v>
       </c>
@@ -35908,7 +35950,7 @@
         <v>5984</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="10">
         <v>46180</v>
       </c>
@@ -35943,7 +35985,7 @@
         <v>6121</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="10">
         <v>46187</v>
       </c>
@@ -35978,7 +36020,7 @@
         <v>6025</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="10">
         <v>46194</v>
       </c>
@@ -36013,7 +36055,7 @@
         <v>6239</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="10">
         <v>46201</v>
       </c>
@@ -36048,7 +36090,7 @@
         <v>5992</v>
       </c>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" s="10">
         <v>46208</v>
       </c>
@@ -36083,7 +36125,7 @@
         <v>5634</v>
       </c>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" s="10">
         <v>46215</v>
       </c>
@@ -36116,6 +36158,41 @@
       </c>
       <c r="K446" s="13">
         <v>5533</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A447" s="10">
+        <v>46222</v>
+      </c>
+      <c r="B447" s="11">
+        <v>46223</v>
+      </c>
+      <c r="C447" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D447" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E447" s="13">
+        <v>2408</v>
+      </c>
+      <c r="F447" s="13">
+        <v>1104</v>
+      </c>
+      <c r="G447" s="13">
+        <v>4009</v>
+      </c>
+      <c r="H447" s="13">
+        <v>1178</v>
+      </c>
+      <c r="I447" s="13">
+        <v>1162</v>
+      </c>
+      <c r="J447" s="13">
+        <v>309</v>
+      </c>
+      <c r="K447" s="13">
+        <v>5473</v>
       </c>
     </row>
   </sheetData>
@@ -36129,7 +36206,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
@@ -36145,12 +36222,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
@@ -36162,7 +36239,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5F5898-C548-4944-945E-5EDED2F0A3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0328BDBB-6F2E-48FC-AFA9-1722FD3BCA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1666,6 +1666,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3012,6 +3015,9 @@
                 </c:pt>
                 <c:pt idx="445">
                   <c:v>2408</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>2393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4393,6 +4399,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5739,6 +5748,9 @@
                 </c:pt>
                 <c:pt idx="445">
                   <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>1020</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7120,6 +7132,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8466,6 +8481,9 @@
                 </c:pt>
                 <c:pt idx="445">
                   <c:v>4009</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9847,6 +9865,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11193,6 +11214,9 @@
                 </c:pt>
                 <c:pt idx="445">
                   <c:v>1178</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>1265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12574,6 +12598,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13920,6 +13947,9 @@
                 </c:pt>
                 <c:pt idx="445">
                   <c:v>1162</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>1113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15303,6 +15333,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16649,6 +16682,9 @@
                 </c:pt>
                 <c:pt idx="445">
                   <c:v>5473</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>5463</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18046,6 +18082,9 @@
                 <c:pt idx="445">
                   <c:v>46223</c:v>
                 </c:pt>
+                <c:pt idx="446">
+                  <c:v>46230</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19391,6 +19430,9 @@
                   <c:v>311</c:v>
                 </c:pt>
                 <c:pt idx="445">
+                  <c:v>309</c:v>
+                </c:pt>
+                <c:pt idx="446">
                   <c:v>309</c:v>
                 </c:pt>
               </c:numCache>
@@ -19453,7 +19495,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -19513,7 +19555,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -19555,7 +19597,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -19624,7 +19666,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -19660,7 +19702,7 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1050">
-          <a:latin typeface="+mn-lt"/>
+          <a:latin typeface="Aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
@@ -20241,10 +20283,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20538,7 +20580,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K447"/>
+  <dimension ref="A1:K448"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
@@ -36193,6 +36235,41 @@
       </c>
       <c r="K447" s="13">
         <v>5473</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A448" s="10">
+        <v>46229</v>
+      </c>
+      <c r="B448" s="11">
+        <v>46230</v>
+      </c>
+      <c r="C448" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D448" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E448" s="13">
+        <v>2393</v>
+      </c>
+      <c r="F448" s="13">
+        <v>1020</v>
+      </c>
+      <c r="G448" s="13">
+        <v>4017</v>
+      </c>
+      <c r="H448" s="13">
+        <v>1265</v>
+      </c>
+      <c r="I448" s="13">
+        <v>1113</v>
+      </c>
+      <c r="J448" s="13">
+        <v>309</v>
+      </c>
+      <c r="K448" s="13">
+        <v>5463</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0328BDBB-6F2E-48FC-AFA9-1722FD3BCA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F3B3DE-17B1-4FA4-8B06-3A1001C7CE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1669,6 +1669,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3018,6 +3021,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>2393</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>2424</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4402,6 +4408,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5751,6 +5760,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7135,6 +7147,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8484,6 +8499,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>4017</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9868,6 +9886,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11217,6 +11238,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>1265</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>950</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12601,6 +12625,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13950,6 +13977,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15336,6 +15366,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16685,6 +16718,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>5463</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>5322</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18085,6 +18121,9 @@
                 <c:pt idx="446">
                   <c:v>46230</c:v>
                 </c:pt>
+                <c:pt idx="447">
+                  <c:v>46237</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19434,6 +19473,9 @@
                 </c:pt>
                 <c:pt idx="446">
                   <c:v>309</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>213</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20580,7 +20622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K448"/>
+  <dimension ref="A1:K449"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
@@ -36270,6 +36312,41 @@
       </c>
       <c r="K448" s="13">
         <v>5463</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A449" s="10">
+        <v>46236</v>
+      </c>
+      <c r="B449" s="11">
+        <v>46237</v>
+      </c>
+      <c r="C449" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D449" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E449" s="13">
+        <v>2424</v>
+      </c>
+      <c r="F449" s="13">
+        <v>1222</v>
+      </c>
+      <c r="G449" s="13">
+        <v>4136</v>
+      </c>
+      <c r="H449" s="13">
+        <v>950</v>
+      </c>
+      <c r="I449" s="13">
+        <v>1296</v>
+      </c>
+      <c r="J449" s="13">
+        <v>213</v>
+      </c>
+      <c r="K449" s="13">
+        <v>5322</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F3B3DE-17B1-4FA4-8B06-3A1001C7CE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE0C228-7446-4378-9E81-681D34906A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1672,6 +1672,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3024,6 +3027,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>2424</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>2420</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4411,6 +4417,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5763,6 +5772,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>1222</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>1094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7150,6 +7162,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8502,6 +8517,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>4136</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9889,6 +9907,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11241,6 +11262,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>1250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12628,6 +12652,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13980,6 +14007,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>1296</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>1255</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15369,6 +15399,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16721,6 +16754,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>5322</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>5409</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18124,6 +18160,9 @@
                 <c:pt idx="447">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="448">
+                  <c:v>46244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19476,6 +19515,9 @@
                 </c:pt>
                 <c:pt idx="447">
                   <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20622,7 +20664,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K449"/>
+  <dimension ref="A1:K450"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
@@ -36347,6 +36389,41 @@
       </c>
       <c r="K449" s="13">
         <v>5322</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A450" s="10">
+        <v>46243</v>
+      </c>
+      <c r="B450" s="11">
+        <v>46244</v>
+      </c>
+      <c r="C450" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D450" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E450" s="13">
+        <v>2420</v>
+      </c>
+      <c r="F450" s="13">
+        <v>1094</v>
+      </c>
+      <c r="G450" s="13">
+        <v>4011</v>
+      </c>
+      <c r="H450" s="13">
+        <v>1250</v>
+      </c>
+      <c r="I450" s="13">
+        <v>1255</v>
+      </c>
+      <c r="J450" s="13">
+        <v>314</v>
+      </c>
+      <c r="K450" s="13">
+        <v>5409</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE0C228-7446-4378-9E81-681D34906A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A868A7-BAB2-4C33-A397-F8E01DB3A4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1675,6 +1675,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3030,6 +3033,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>2420</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>2425</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4420,6 +4426,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5775,6 +5784,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>1094</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>1055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7165,6 +7177,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8520,6 +8535,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>4011</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9910,6 +9928,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11265,6 +11286,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>1144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12655,6 +12679,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14010,6 +14037,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>1255</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>1293</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15402,6 +15432,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16757,6 +16790,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>5409</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>5383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18163,6 +18199,9 @@
                 <c:pt idx="448">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="449">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19518,6 +19557,9 @@
                 </c:pt>
                 <c:pt idx="448">
                   <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>252</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20664,7 +20706,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K451"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
@@ -36424,6 +36466,41 @@
       </c>
       <c r="K450" s="13">
         <v>5409</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A451" s="10">
+        <v>46250</v>
+      </c>
+      <c r="B451" s="11">
+        <v>46251</v>
+      </c>
+      <c r="C451" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D451" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E451" s="13">
+        <v>2425</v>
+      </c>
+      <c r="F451" s="13">
+        <v>1055</v>
+      </c>
+      <c r="G451" s="13">
+        <v>4147</v>
+      </c>
+      <c r="H451" s="13">
+        <v>1144</v>
+      </c>
+      <c r="I451" s="13">
+        <v>1293</v>
+      </c>
+      <c r="J451" s="13">
+        <v>252</v>
+      </c>
+      <c r="K451" s="13">
+        <v>5383</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A868A7-BAB2-4C33-A397-F8E01DB3A4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77478159-BD8A-7B49-85DC-89AFD89C351B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17920" yWindow="780" windowWidth="18080" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
     <sheet name="fig" sheetId="3" r:id="rId2"/>
     <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -109,29 +109,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -153,7 +153,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -170,7 +170,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -214,7 +214,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -235,33 +235,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -279,7 +279,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1678,6 +1678,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3036,6 +3039,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>2425</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>2419</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4429,6 +4435,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5787,6 +5796,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>1055</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7180,6 +7192,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8538,6 +8553,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>4147</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9931,6 +9949,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11289,6 +11310,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>1144</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1056</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12682,6 +12706,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14040,6 +14067,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>1293</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15435,6 +15465,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16793,6 +16826,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>5383</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>5206</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18202,6 +18238,9 @@
                 <c:pt idx="449">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="450">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19560,6 +19599,9 @@
                 </c:pt>
                 <c:pt idx="449">
                   <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20706,19 +20748,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K451"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K452"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="7.19921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="7.1640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" style="13" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
@@ -20753,7 +20795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="10">
         <v>43100</v>
       </c>
@@ -20788,7 +20830,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="10">
         <v>43107</v>
       </c>
@@ -20823,7 +20865,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4" s="10">
         <v>43114</v>
       </c>
@@ -20858,7 +20900,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="10">
         <v>43121</v>
       </c>
@@ -20893,7 +20935,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="10">
         <v>43128</v>
       </c>
@@ -20928,7 +20970,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7" s="10">
         <v>43135</v>
       </c>
@@ -20963,7 +21005,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" s="10">
         <v>43142</v>
       </c>
@@ -20998,7 +21040,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" s="10">
         <v>43149</v>
       </c>
@@ -21033,7 +21075,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" s="10">
         <v>43156</v>
       </c>
@@ -21068,7 +21110,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="10">
         <v>43163</v>
       </c>
@@ -21103,7 +21145,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" s="10">
         <v>43170</v>
       </c>
@@ -21138,7 +21180,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" s="10">
         <v>43177</v>
       </c>
@@ -21173,7 +21215,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14" s="10">
         <v>43184</v>
       </c>
@@ -21208,7 +21250,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15" s="10">
         <v>43191</v>
       </c>
@@ -21243,7 +21285,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="10">
         <v>43198</v>
       </c>
@@ -21278,7 +21320,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
         <v>43205</v>
       </c>
@@ -21313,7 +21355,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
         <v>43212</v>
       </c>
@@ -21348,7 +21390,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
         <v>43219</v>
       </c>
@@ -21383,7 +21425,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
         <v>43226</v>
       </c>
@@ -21418,7 +21460,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
         <v>43233</v>
       </c>
@@ -21453,7 +21495,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
         <v>43240</v>
       </c>
@@ -21488,7 +21530,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
         <v>43247</v>
       </c>
@@ -21523,7 +21565,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
         <v>43254</v>
       </c>
@@ -21558,7 +21600,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
         <v>43261</v>
       </c>
@@ -21593,7 +21635,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
         <v>43268</v>
       </c>
@@ -21628,7 +21670,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
         <v>43275</v>
       </c>
@@ -21663,7 +21705,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
         <v>43282</v>
       </c>
@@ -21698,7 +21740,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
         <v>43289</v>
       </c>
@@ -21733,7 +21775,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
         <v>43296</v>
       </c>
@@ -21768,7 +21810,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
         <v>43303</v>
       </c>
@@ -21803,7 +21845,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
         <v>43310</v>
       </c>
@@ -21838,7 +21880,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
         <v>43317</v>
       </c>
@@ -21873,7 +21915,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34" s="10">
         <v>43324</v>
       </c>
@@ -21908,7 +21950,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="10">
         <v>43331</v>
       </c>
@@ -21943,7 +21985,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36" s="10">
         <v>43338</v>
       </c>
@@ -21978,7 +22020,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="10">
         <v>43345</v>
       </c>
@@ -22013,7 +22055,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38" s="10">
         <v>43352</v>
       </c>
@@ -22048,7 +22090,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" s="10">
         <v>43359</v>
       </c>
@@ -22083,7 +22125,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40" s="10">
         <v>43366</v>
       </c>
@@ -22118,7 +22160,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41" s="10">
         <v>43373</v>
       </c>
@@ -22153,7 +22195,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42" s="10">
         <v>43380</v>
       </c>
@@ -22188,7 +22230,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43" s="10">
         <v>43387</v>
       </c>
@@ -22223,7 +22265,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44" s="10">
         <v>43394</v>
       </c>
@@ -22258,7 +22300,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45" s="10">
         <v>43401</v>
       </c>
@@ -22293,7 +22335,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46" s="10">
         <v>43408</v>
       </c>
@@ -22328,7 +22370,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47" s="10">
         <v>43415</v>
       </c>
@@ -22363,7 +22405,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48" s="10">
         <v>43422</v>
       </c>
@@ -22398,7 +22440,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49" s="10">
         <v>43429</v>
       </c>
@@ -22433,7 +22475,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11">
       <c r="A50" s="10">
         <v>43436</v>
       </c>
@@ -22468,7 +22510,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11">
       <c r="A51" s="10">
         <v>43443</v>
       </c>
@@ -22503,7 +22545,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11">
       <c r="A52" s="10">
         <v>43450</v>
       </c>
@@ -22538,7 +22580,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11">
       <c r="A53" s="10">
         <v>43457</v>
       </c>
@@ -22573,7 +22615,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11">
       <c r="A54" s="10">
         <v>43464</v>
       </c>
@@ -22608,7 +22650,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11">
       <c r="A55" s="10">
         <v>43471</v>
       </c>
@@ -22643,7 +22685,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11">
       <c r="A56" s="10">
         <v>43478</v>
       </c>
@@ -22678,7 +22720,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11">
       <c r="A57" s="10">
         <v>43485</v>
       </c>
@@ -22713,7 +22755,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11">
       <c r="A58" s="10">
         <v>43492</v>
       </c>
@@ -22748,7 +22790,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11">
       <c r="A59" s="10">
         <v>43499</v>
       </c>
@@ -22783,7 +22825,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11">
       <c r="A60" s="10">
         <v>43506</v>
       </c>
@@ -22818,7 +22860,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11">
       <c r="A61" s="10">
         <v>43513</v>
       </c>
@@ -22853,7 +22895,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11">
       <c r="A62" s="10">
         <v>43520</v>
       </c>
@@ -22888,7 +22930,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11">
       <c r="A63" s="10">
         <v>43527</v>
       </c>
@@ -22923,7 +22965,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11">
       <c r="A64" s="10">
         <v>43534</v>
       </c>
@@ -22958,7 +23000,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11">
       <c r="A65" s="10">
         <v>43541</v>
       </c>
@@ -22993,7 +23035,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11">
       <c r="A66" s="10">
         <v>43548</v>
       </c>
@@ -23028,7 +23070,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
       <c r="A67" s="10">
         <v>43555</v>
       </c>
@@ -23063,7 +23105,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
       <c r="A68" s="10">
         <v>43562</v>
       </c>
@@ -23098,7 +23140,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11">
       <c r="A69" s="10">
         <v>43569</v>
       </c>
@@ -23133,7 +23175,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="A70" s="10">
         <v>43576</v>
       </c>
@@ -23168,7 +23210,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="A71" s="10">
         <v>43583</v>
       </c>
@@ -23203,7 +23245,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="A72" s="10">
         <v>43590</v>
       </c>
@@ -23238,7 +23280,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11">
       <c r="A73" s="10">
         <v>43597</v>
       </c>
@@ -23273,7 +23315,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11">
       <c r="A74" s="10">
         <v>43604</v>
       </c>
@@ -23308,7 +23350,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11">
       <c r="A75" s="10">
         <v>43611</v>
       </c>
@@ -23343,7 +23385,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11">
       <c r="A76" s="10">
         <v>43618</v>
       </c>
@@ -23378,7 +23420,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11">
       <c r="A77" s="10">
         <v>43625</v>
       </c>
@@ -23413,7 +23455,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11">
       <c r="A78" s="10">
         <v>43632</v>
       </c>
@@ -23448,7 +23490,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11">
       <c r="A79" s="10">
         <v>43639</v>
       </c>
@@ -23483,7 +23525,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="A80" s="10">
         <v>43646</v>
       </c>
@@ -23518,7 +23560,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11">
       <c r="A81" s="10">
         <v>43653</v>
       </c>
@@ -23553,7 +23595,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11">
       <c r="A82" s="10">
         <v>43660</v>
       </c>
@@ -23588,7 +23630,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11">
       <c r="A83" s="10">
         <v>43667</v>
       </c>
@@ -23623,7 +23665,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11">
       <c r="A84" s="10">
         <v>43674</v>
       </c>
@@ -23658,7 +23700,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11">
       <c r="A85" s="10">
         <v>43681</v>
       </c>
@@ -23693,7 +23735,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11">
       <c r="A86" s="10">
         <v>43688</v>
       </c>
@@ -23728,7 +23770,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11">
       <c r="A87" s="10">
         <v>43695</v>
       </c>
@@ -23763,7 +23805,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11">
       <c r="A88" s="10">
         <v>43702</v>
       </c>
@@ -23798,7 +23840,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11">
       <c r="A89" s="10">
         <v>43709</v>
       </c>
@@ -23833,7 +23875,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11">
       <c r="A90" s="10">
         <v>43716</v>
       </c>
@@ -23868,7 +23910,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11">
       <c r="A91" s="10">
         <v>43723</v>
       </c>
@@ -23903,7 +23945,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11">
       <c r="A92" s="10">
         <v>43730</v>
       </c>
@@ -23938,7 +23980,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11">
       <c r="A93" s="10">
         <v>43737</v>
       </c>
@@ -23973,7 +24015,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11">
       <c r="A94" s="10">
         <v>43744</v>
       </c>
@@ -24008,7 +24050,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11">
       <c r="A95" s="10">
         <v>43751</v>
       </c>
@@ -24043,7 +24085,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11">
       <c r="A96" s="10">
         <v>43758</v>
       </c>
@@ -24078,7 +24120,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11">
       <c r="A97" s="10">
         <v>43765</v>
       </c>
@@ -24113,7 +24155,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11">
       <c r="A98" s="10">
         <v>43772</v>
       </c>
@@ -24148,7 +24190,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11">
       <c r="A99" s="10">
         <v>43779</v>
       </c>
@@ -24183,7 +24225,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11">
       <c r="A100" s="10">
         <v>43786</v>
       </c>
@@ -24218,7 +24260,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11">
       <c r="A101" s="10">
         <v>43793</v>
       </c>
@@ -24253,7 +24295,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11">
       <c r="A102" s="10">
         <v>43800</v>
       </c>
@@ -24288,7 +24330,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11">
       <c r="A103" s="10">
         <v>43807</v>
       </c>
@@ -24323,7 +24365,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11">
       <c r="A104" s="10">
         <v>43814</v>
       </c>
@@ -24358,7 +24400,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11">
       <c r="A105" s="10">
         <v>43821</v>
       </c>
@@ -24393,7 +24435,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11">
       <c r="A106" s="10">
         <v>43828</v>
       </c>
@@ -24428,7 +24470,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11">
       <c r="A107" s="10">
         <v>43835</v>
       </c>
@@ -24463,7 +24505,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11">
       <c r="A108" s="10">
         <v>43842</v>
       </c>
@@ -24498,7 +24540,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11">
       <c r="A109" s="10">
         <v>43849</v>
       </c>
@@ -24533,7 +24575,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11">
       <c r="A110" s="10">
         <v>43856</v>
       </c>
@@ -24568,7 +24610,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11">
       <c r="A111" s="10">
         <v>43863</v>
       </c>
@@ -24603,7 +24645,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11">
       <c r="A112" s="10">
         <v>43870</v>
       </c>
@@ -24638,7 +24680,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11">
       <c r="A113" s="10">
         <v>43877</v>
       </c>
@@ -24673,7 +24715,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11">
       <c r="A114" s="10">
         <v>43884</v>
       </c>
@@ -24708,7 +24750,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11">
       <c r="A115" s="10">
         <v>43891</v>
       </c>
@@ -24743,7 +24785,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11">
       <c r="A116" s="10">
         <v>43898</v>
       </c>
@@ -24778,7 +24820,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11">
       <c r="A117" s="10">
         <v>43905</v>
       </c>
@@ -24813,7 +24855,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11">
       <c r="A118" s="10">
         <v>43912</v>
       </c>
@@ -24848,7 +24890,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11">
       <c r="A119" s="10">
         <v>43919</v>
       </c>
@@ -24883,7 +24925,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11">
       <c r="A120" s="10">
         <v>43926</v>
       </c>
@@ -24918,7 +24960,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11">
       <c r="A121" s="10">
         <v>43933</v>
       </c>
@@ -24953,7 +24995,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11">
       <c r="A122" s="10">
         <v>43940</v>
       </c>
@@ -24988,7 +25030,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11">
       <c r="A123" s="10">
         <v>43947</v>
       </c>
@@ -25023,7 +25065,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11">
       <c r="A124" s="10">
         <v>43954</v>
       </c>
@@ -25058,7 +25100,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11">
       <c r="A125" s="10">
         <v>43961</v>
       </c>
@@ -25093,7 +25135,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11">
       <c r="A126" s="10">
         <v>43968</v>
       </c>
@@ -25128,7 +25170,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11">
       <c r="A127" s="10">
         <v>43975</v>
       </c>
@@ -25163,7 +25205,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11">
       <c r="A128" s="10">
         <v>43982</v>
       </c>
@@ -25198,7 +25240,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11">
       <c r="A129" s="10">
         <v>43989</v>
       </c>
@@ -25233,7 +25275,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11">
       <c r="A130" s="10">
         <v>43996</v>
       </c>
@@ -25268,7 +25310,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11">
       <c r="A131" s="10">
         <v>44003</v>
       </c>
@@ -25303,7 +25345,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11">
       <c r="A132" s="10">
         <v>44010</v>
       </c>
@@ -25338,7 +25380,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11">
       <c r="A133" s="10">
         <v>44017</v>
       </c>
@@ -25373,7 +25415,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11">
       <c r="A134" s="10">
         <v>44024</v>
       </c>
@@ -25408,7 +25450,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11">
       <c r="A135" s="10">
         <v>44031</v>
       </c>
@@ -25443,7 +25485,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11">
       <c r="A136" s="10">
         <v>44038</v>
       </c>
@@ -25478,7 +25520,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11">
       <c r="A137" s="10">
         <v>44045</v>
       </c>
@@ -25513,7 +25555,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11">
       <c r="A138" s="10">
         <v>44052</v>
       </c>
@@ -25548,7 +25590,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11">
       <c r="A139" s="10">
         <v>44059</v>
       </c>
@@ -25583,7 +25625,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11">
       <c r="A140" s="10">
         <v>44066</v>
       </c>
@@ -25618,7 +25660,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11">
       <c r="A141" s="10">
         <v>44073</v>
       </c>
@@ -25653,7 +25695,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11">
       <c r="A142" s="10">
         <v>44080</v>
       </c>
@@ -25688,7 +25730,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11">
       <c r="A143" s="10">
         <v>44087</v>
       </c>
@@ -25723,7 +25765,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11">
       <c r="A144" s="10">
         <v>44094</v>
       </c>
@@ -25758,7 +25800,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11">
       <c r="A145" s="10">
         <v>44101</v>
       </c>
@@ -25793,7 +25835,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11">
       <c r="A146" s="10">
         <v>44108</v>
       </c>
@@ -25828,7 +25870,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11">
       <c r="A147" s="10">
         <v>44115</v>
       </c>
@@ -25863,7 +25905,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11">
       <c r="A148" s="10">
         <v>44122</v>
       </c>
@@ -25898,7 +25940,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11">
       <c r="A149" s="10">
         <v>44129</v>
       </c>
@@ -25933,7 +25975,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11">
       <c r="A150" s="10">
         <v>44136</v>
       </c>
@@ -25968,7 +26010,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11">
       <c r="A151" s="10">
         <v>44143</v>
       </c>
@@ -26003,7 +26045,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11">
       <c r="A152" s="10">
         <v>44150</v>
       </c>
@@ -26038,7 +26080,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11">
       <c r="A153" s="10">
         <v>44157</v>
       </c>
@@ -26073,7 +26115,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11">
       <c r="A154" s="10">
         <v>44164</v>
       </c>
@@ -26108,7 +26150,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11">
       <c r="A155" s="10">
         <v>44171</v>
       </c>
@@ -26143,7 +26185,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11">
       <c r="A156" s="10">
         <v>44178</v>
       </c>
@@ -26178,7 +26220,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11">
       <c r="A157" s="10">
         <v>44185</v>
       </c>
@@ -26213,7 +26255,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11">
       <c r="A158" s="10">
         <v>44192</v>
       </c>
@@ -26248,7 +26290,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11">
       <c r="A159" s="10">
         <v>44199</v>
       </c>
@@ -26283,7 +26325,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11">
       <c r="A160" s="10">
         <v>44206</v>
       </c>
@@ -26318,7 +26360,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11">
       <c r="A161" s="10">
         <v>44213</v>
       </c>
@@ -26353,7 +26395,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11">
       <c r="A162" s="10">
         <v>44220</v>
       </c>
@@ -26388,7 +26430,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11">
       <c r="A163" s="10">
         <v>44227</v>
       </c>
@@ -26423,7 +26465,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11">
       <c r="A164" s="10">
         <v>44234</v>
       </c>
@@ -26458,7 +26500,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11">
       <c r="A165" s="10">
         <v>44241</v>
       </c>
@@ -26493,7 +26535,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11">
       <c r="A166" s="10">
         <v>44248</v>
       </c>
@@ -26528,7 +26570,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11">
       <c r="A167" s="10">
         <v>44255</v>
       </c>
@@ -26563,7 +26605,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11">
       <c r="A168" s="10">
         <v>44262</v>
       </c>
@@ -26598,7 +26640,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11">
       <c r="A169" s="10">
         <v>44269</v>
       </c>
@@ -26633,7 +26675,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11">
       <c r="A170" s="10">
         <v>44276</v>
       </c>
@@ -26668,7 +26710,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11">
       <c r="A171" s="10">
         <v>44283</v>
       </c>
@@ -26703,7 +26745,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11">
       <c r="A172" s="10">
         <v>44290</v>
       </c>
@@ -26738,7 +26780,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11">
       <c r="A173" s="10">
         <v>44297</v>
       </c>
@@ -26773,7 +26815,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11">
       <c r="A174" s="10">
         <v>44304</v>
       </c>
@@ -26808,7 +26850,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11">
       <c r="A175" s="10">
         <v>44311</v>
       </c>
@@ -26843,7 +26885,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11">
       <c r="A176" s="10">
         <v>44318</v>
       </c>
@@ -26878,7 +26920,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11">
       <c r="A177" s="10">
         <v>44325</v>
       </c>
@@ -26913,7 +26955,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11">
       <c r="A178" s="10">
         <v>44332</v>
       </c>
@@ -26948,7 +26990,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11">
       <c r="A179" s="10">
         <v>44339</v>
       </c>
@@ -26983,7 +27025,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11">
       <c r="A180" s="10">
         <v>44346</v>
       </c>
@@ -27018,7 +27060,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11">
       <c r="A181" s="10">
         <v>44353</v>
       </c>
@@ -27053,7 +27095,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11">
       <c r="A182" s="10">
         <v>44360</v>
       </c>
@@ -27088,7 +27130,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11">
       <c r="A183" s="10">
         <v>44367</v>
       </c>
@@ -27123,7 +27165,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11">
       <c r="A184" s="10">
         <v>44374</v>
       </c>
@@ -27158,7 +27200,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11">
       <c r="A185" s="10">
         <v>44381</v>
       </c>
@@ -27193,7 +27235,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11">
       <c r="A186" s="10">
         <v>44388</v>
       </c>
@@ -27228,7 +27270,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11">
       <c r="A187" s="10">
         <v>44395</v>
       </c>
@@ -27263,7 +27305,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11">
       <c r="A188" s="10">
         <v>44402</v>
       </c>
@@ -27298,7 +27340,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11">
       <c r="A189" s="10">
         <v>44409</v>
       </c>
@@ -27333,7 +27375,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11">
       <c r="A190" s="10">
         <v>44416</v>
       </c>
@@ -27368,7 +27410,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11">
       <c r="A191" s="10">
         <v>44423</v>
       </c>
@@ -27403,7 +27445,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11">
       <c r="A192" s="10">
         <v>44430</v>
       </c>
@@ -27438,7 +27480,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11">
       <c r="A193" s="10">
         <v>44437</v>
       </c>
@@ -27473,7 +27515,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11">
       <c r="A194" s="10">
         <v>44444</v>
       </c>
@@ -27508,7 +27550,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11">
       <c r="A195" s="10">
         <v>44451</v>
       </c>
@@ -27543,7 +27585,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11">
       <c r="A196" s="10">
         <v>44458</v>
       </c>
@@ -27578,7 +27620,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11">
       <c r="A197" s="10">
         <v>44465</v>
       </c>
@@ -27613,7 +27655,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11">
       <c r="A198" s="10">
         <v>44472</v>
       </c>
@@ -27648,7 +27690,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11">
       <c r="A199" s="10">
         <v>44479</v>
       </c>
@@ -27683,7 +27725,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11">
       <c r="A200" s="10">
         <v>44486</v>
       </c>
@@ -27718,7 +27760,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11">
       <c r="A201" s="10">
         <v>44493</v>
       </c>
@@ -27753,7 +27795,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11">
       <c r="A202" s="10">
         <v>44500</v>
       </c>
@@ -27788,7 +27830,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11">
       <c r="A203" s="10">
         <v>44507</v>
       </c>
@@ -27823,7 +27865,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11">
       <c r="A204" s="10">
         <v>44514</v>
       </c>
@@ -27858,7 +27900,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11">
       <c r="A205" s="10">
         <v>44521</v>
       </c>
@@ -27893,7 +27935,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11">
       <c r="A206" s="10">
         <v>44528</v>
       </c>
@@ -27928,7 +27970,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11">
       <c r="A207" s="10">
         <v>44535</v>
       </c>
@@ -27963,7 +28005,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11">
       <c r="A208" s="10">
         <v>44542</v>
       </c>
@@ -27998,7 +28040,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11">
       <c r="A209" s="10">
         <v>44549</v>
       </c>
@@ -28033,7 +28075,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11">
       <c r="A210" s="10">
         <v>44556</v>
       </c>
@@ -28068,7 +28110,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11">
       <c r="A211" s="10">
         <v>44563</v>
       </c>
@@ -28103,7 +28145,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11">
       <c r="A212" s="10">
         <v>44570</v>
       </c>
@@ -28138,7 +28180,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11">
       <c r="A213" s="10">
         <v>44577</v>
       </c>
@@ -28173,7 +28215,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11">
       <c r="A214" s="10">
         <v>44584</v>
       </c>
@@ -28208,7 +28250,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11">
       <c r="A215" s="10">
         <v>44591</v>
       </c>
@@ -28243,7 +28285,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11">
       <c r="A216" s="10">
         <v>44598</v>
       </c>
@@ -28278,7 +28320,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11">
       <c r="A217" s="10">
         <v>44605</v>
       </c>
@@ -28313,7 +28355,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11">
       <c r="A218" s="10">
         <v>44612</v>
       </c>
@@ -28348,7 +28390,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11">
       <c r="A219" s="10">
         <v>44619</v>
       </c>
@@ -28383,7 +28425,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11">
       <c r="A220" s="10">
         <v>44626</v>
       </c>
@@ -28418,7 +28460,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11">
       <c r="A221" s="10">
         <v>44633</v>
       </c>
@@ -28453,7 +28495,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11">
       <c r="A222" s="10">
         <v>44640</v>
       </c>
@@ -28488,7 +28530,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11">
       <c r="A223" s="10">
         <v>44647</v>
       </c>
@@ -28523,7 +28565,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11">
       <c r="A224" s="10">
         <v>44654</v>
       </c>
@@ -28558,7 +28600,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11">
       <c r="A225" s="10">
         <v>44661</v>
       </c>
@@ -28593,7 +28635,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11">
       <c r="A226" s="10">
         <v>44668</v>
       </c>
@@ -28628,7 +28670,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11">
       <c r="A227" s="10">
         <v>44675</v>
       </c>
@@ -28663,7 +28705,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11">
       <c r="A228" s="10">
         <v>44682</v>
       </c>
@@ -28698,7 +28740,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11">
       <c r="A229" s="10">
         <v>44689</v>
       </c>
@@ -28733,7 +28775,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11">
       <c r="A230" s="10">
         <v>44696</v>
       </c>
@@ -28768,7 +28810,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11">
       <c r="A231" s="10">
         <v>44703</v>
       </c>
@@ -28803,7 +28845,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11">
       <c r="A232" s="10">
         <v>44710</v>
       </c>
@@ -28838,7 +28880,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11">
       <c r="A233" s="10">
         <v>44717</v>
       </c>
@@ -28873,7 +28915,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11">
       <c r="A234" s="10">
         <v>44724</v>
       </c>
@@ -28908,7 +28950,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11">
       <c r="A235" s="10">
         <v>44731</v>
       </c>
@@ -28943,7 +28985,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11">
       <c r="A236" s="10">
         <v>44738</v>
       </c>
@@ -28978,7 +29020,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11">
       <c r="A237" s="10">
         <v>44745</v>
       </c>
@@ -29013,7 +29055,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11">
       <c r="A238" s="10">
         <v>44752</v>
       </c>
@@ -29048,7 +29090,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11">
       <c r="A239" s="10">
         <v>44759</v>
       </c>
@@ -29083,7 +29125,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11">
       <c r="A240" s="10">
         <v>44766</v>
       </c>
@@ -29118,7 +29160,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11">
       <c r="A241" s="10">
         <v>44773</v>
       </c>
@@ -29153,7 +29195,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11">
       <c r="A242" s="10">
         <v>44780</v>
       </c>
@@ -29188,7 +29230,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11">
       <c r="A243" s="10">
         <v>44787</v>
       </c>
@@ -29223,7 +29265,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11">
       <c r="A244" s="10">
         <v>44794</v>
       </c>
@@ -29258,7 +29300,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11">
       <c r="A245" s="10">
         <v>44801</v>
       </c>
@@ -29293,7 +29335,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11">
       <c r="A246" s="10">
         <v>44808</v>
       </c>
@@ -29328,7 +29370,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11">
       <c r="A247" s="10">
         <v>44815</v>
       </c>
@@ -29363,7 +29405,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11">
       <c r="A248" s="10">
         <v>44822</v>
       </c>
@@ -29398,7 +29440,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11">
       <c r="A249" s="10">
         <v>44829</v>
       </c>
@@ -29433,7 +29475,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11">
       <c r="A250" s="10">
         <v>44836</v>
       </c>
@@ -29468,7 +29510,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11">
       <c r="A251" s="10">
         <v>44843</v>
       </c>
@@ -29503,7 +29545,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11">
       <c r="A252" s="10">
         <v>44850</v>
       </c>
@@ -29538,7 +29580,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11">
       <c r="A253" s="10">
         <v>44857</v>
       </c>
@@ -29573,7 +29615,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11">
       <c r="A254" s="10">
         <v>44864</v>
       </c>
@@ -29608,7 +29650,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11">
       <c r="A255" s="10">
         <v>44871</v>
       </c>
@@ -29643,7 +29685,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11">
       <c r="A256" s="10">
         <v>44878</v>
       </c>
@@ -29678,7 +29720,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11">
       <c r="A257" s="10">
         <v>44885</v>
       </c>
@@ -29713,7 +29755,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11">
       <c r="A258" s="10">
         <v>44892</v>
       </c>
@@ -29748,7 +29790,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11">
       <c r="A259" s="10">
         <v>44899</v>
       </c>
@@ -29783,7 +29825,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11">
       <c r="A260" s="10">
         <v>44906</v>
       </c>
@@ -29818,7 +29860,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11">
       <c r="A261" s="10">
         <v>44913</v>
       </c>
@@ -29853,7 +29895,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11">
       <c r="A262" s="10">
         <v>44920</v>
       </c>
@@ -29888,7 +29930,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11">
       <c r="A263" s="10">
         <v>44927</v>
       </c>
@@ -29923,7 +29965,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11">
       <c r="A264" s="10">
         <v>44934</v>
       </c>
@@ -29958,7 +30000,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11">
       <c r="A265" s="10">
         <v>44941</v>
       </c>
@@ -29993,7 +30035,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11">
       <c r="A266" s="10">
         <v>44948</v>
       </c>
@@ -30028,7 +30070,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11">
       <c r="A267" s="10">
         <v>44955</v>
       </c>
@@ -30063,7 +30105,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11">
       <c r="A268" s="10">
         <v>44962</v>
       </c>
@@ -30098,7 +30140,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11">
       <c r="A269" s="10">
         <v>44969</v>
       </c>
@@ -30133,7 +30175,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11">
       <c r="A270" s="10">
         <v>44976</v>
       </c>
@@ -30168,7 +30210,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11">
       <c r="A271" s="10">
         <v>44983</v>
       </c>
@@ -30203,7 +30245,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11">
       <c r="A272" s="10">
         <v>44990</v>
       </c>
@@ -30238,7 +30280,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11">
       <c r="A273" s="10">
         <v>44997</v>
       </c>
@@ -30273,7 +30315,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11">
       <c r="A274" s="10">
         <v>45004</v>
       </c>
@@ -30308,7 +30350,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11">
       <c r="A275" s="10">
         <v>45011</v>
       </c>
@@ -30343,7 +30385,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11">
       <c r="A276" s="10">
         <v>45018</v>
       </c>
@@ -30378,7 +30420,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11">
       <c r="A277" s="10">
         <v>45025</v>
       </c>
@@ -30413,7 +30455,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11">
       <c r="A278" s="10">
         <v>45032</v>
       </c>
@@ -30448,7 +30490,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11">
       <c r="A279" s="10">
         <v>45039</v>
       </c>
@@ -30483,7 +30525,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11">
       <c r="A280" s="10">
         <v>45046</v>
       </c>
@@ -30518,7 +30560,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11">
       <c r="A281" s="10">
         <v>45053</v>
       </c>
@@ -30553,7 +30595,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11">
       <c r="A282" s="10">
         <v>45060</v>
       </c>
@@ -30588,7 +30630,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11">
       <c r="A283" s="10">
         <v>45067</v>
       </c>
@@ -30623,7 +30665,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11">
       <c r="A284" s="10">
         <v>45074</v>
       </c>
@@ -30658,7 +30700,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11">
       <c r="A285" s="10">
         <v>45081</v>
       </c>
@@ -30693,7 +30735,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11">
       <c r="A286" s="10">
         <v>45088</v>
       </c>
@@ -30728,7 +30770,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11">
       <c r="A287" s="10">
         <v>45095</v>
       </c>
@@ -30763,7 +30805,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11">
       <c r="A288" s="10">
         <v>45102</v>
       </c>
@@ -30798,7 +30840,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11">
       <c r="A289" s="10">
         <v>45109</v>
       </c>
@@ -30833,7 +30875,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11">
       <c r="A290" s="10">
         <v>45116</v>
       </c>
@@ -30868,7 +30910,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11">
       <c r="A291" s="10">
         <v>45123</v>
       </c>
@@ -30903,7 +30945,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11">
       <c r="A292" s="10">
         <v>45130</v>
       </c>
@@ -30938,7 +30980,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11">
       <c r="A293" s="10">
         <v>45137</v>
       </c>
@@ -30973,7 +31015,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11">
       <c r="A294" s="10">
         <v>45144</v>
       </c>
@@ -31008,7 +31050,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11">
       <c r="A295" s="10">
         <v>45151</v>
       </c>
@@ -31043,7 +31085,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11">
       <c r="A296" s="10">
         <v>45158</v>
       </c>
@@ -31078,7 +31120,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11">
       <c r="A297" s="10">
         <v>45165</v>
       </c>
@@ -31113,7 +31155,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11">
       <c r="A298" s="10">
         <v>45172</v>
       </c>
@@ -31148,7 +31190,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11">
       <c r="A299" s="10">
         <v>45179</v>
       </c>
@@ -31183,7 +31225,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11">
       <c r="A300" s="10">
         <v>45186</v>
       </c>
@@ -31218,7 +31260,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11">
       <c r="A301" s="10">
         <v>45193</v>
       </c>
@@ -31253,7 +31295,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11">
       <c r="A302" s="10">
         <v>45200</v>
       </c>
@@ -31288,7 +31330,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11">
       <c r="A303" s="10">
         <v>45207</v>
       </c>
@@ -31323,7 +31365,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11">
       <c r="A304" s="10">
         <v>45214</v>
       </c>
@@ -31358,7 +31400,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11">
       <c r="A305" s="10">
         <v>45221</v>
       </c>
@@ -31393,7 +31435,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11">
       <c r="A306" s="10">
         <v>45228</v>
       </c>
@@ -31428,7 +31470,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11">
       <c r="A307" s="10">
         <v>45235</v>
       </c>
@@ -31463,7 +31505,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11">
       <c r="A308" s="10">
         <v>45242</v>
       </c>
@@ -31498,7 +31540,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11">
       <c r="A309" s="10">
         <v>45249</v>
       </c>
@@ -31533,7 +31575,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11">
       <c r="A310" s="10">
         <v>45256</v>
       </c>
@@ -31568,7 +31610,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11">
       <c r="A311" s="10">
         <v>45263</v>
       </c>
@@ -31603,7 +31645,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11">
       <c r="A312" s="10">
         <v>45270</v>
       </c>
@@ -31638,7 +31680,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11">
       <c r="A313" s="10">
         <v>45277</v>
       </c>
@@ -31673,7 +31715,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11">
       <c r="A314" s="10">
         <v>45284</v>
       </c>
@@ -31708,7 +31750,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11">
       <c r="A315" s="10">
         <v>45291</v>
       </c>
@@ -31743,7 +31785,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11">
       <c r="A316" s="10">
         <v>45298</v>
       </c>
@@ -31778,7 +31820,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11">
       <c r="A317" s="10">
         <v>45305</v>
       </c>
@@ -31813,7 +31855,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11">
       <c r="A318" s="10">
         <v>45312</v>
       </c>
@@ -31848,7 +31890,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11">
       <c r="A319" s="10">
         <v>45319</v>
       </c>
@@ -31883,7 +31925,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11">
       <c r="A320" s="10">
         <v>45326</v>
       </c>
@@ -31918,7 +31960,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11">
       <c r="A321" s="10">
         <v>45333</v>
       </c>
@@ -31953,7 +31995,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11">
       <c r="A322" s="10">
         <v>45340</v>
       </c>
@@ -31988,7 +32030,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11">
       <c r="A323" s="10">
         <v>45347</v>
       </c>
@@ -32023,7 +32065,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11">
       <c r="A324" s="10">
         <v>45354</v>
       </c>
@@ -32058,7 +32100,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11">
       <c r="A325" s="10">
         <v>45361</v>
       </c>
@@ -32093,7 +32135,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11">
       <c r="A326" s="10">
         <v>45368</v>
       </c>
@@ -32128,7 +32170,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11">
       <c r="A327" s="10">
         <v>45375</v>
       </c>
@@ -32163,7 +32205,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11">
       <c r="A328" s="10">
         <v>45382</v>
       </c>
@@ -32198,7 +32240,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11">
       <c r="A329" s="10">
         <v>45389</v>
       </c>
@@ -32233,7 +32275,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11">
       <c r="A330" s="10">
         <v>45396</v>
       </c>
@@ -32268,7 +32310,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11">
       <c r="A331" s="10">
         <v>45403</v>
       </c>
@@ -32303,7 +32345,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11">
       <c r="A332" s="10">
         <v>45410</v>
       </c>
@@ -32338,7 +32380,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11">
       <c r="A333" s="10">
         <v>45417</v>
       </c>
@@ -32373,7 +32415,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11">
       <c r="A334" s="10">
         <v>45424</v>
       </c>
@@ -32408,7 +32450,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11">
       <c r="A335" s="10">
         <v>45431</v>
       </c>
@@ -32443,7 +32485,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11">
       <c r="A336" s="10">
         <v>45438</v>
       </c>
@@ -32478,7 +32520,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11">
       <c r="A337" s="10">
         <v>45445</v>
       </c>
@@ -32513,7 +32555,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11">
       <c r="A338" s="10">
         <v>45452</v>
       </c>
@@ -32548,7 +32590,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11">
       <c r="A339" s="10">
         <v>45459</v>
       </c>
@@ -32583,7 +32625,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11">
       <c r="A340" s="10">
         <v>45466</v>
       </c>
@@ -32618,7 +32660,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11">
       <c r="A341" s="10">
         <v>45473</v>
       </c>
@@ -32653,7 +32695,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11">
       <c r="A342" s="10">
         <v>45480</v>
       </c>
@@ -32688,7 +32730,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11">
       <c r="A343" s="10">
         <v>45487</v>
       </c>
@@ -32723,7 +32765,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11">
       <c r="A344" s="10">
         <v>45494</v>
       </c>
@@ -32758,7 +32800,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11">
       <c r="A345" s="10">
         <v>45501</v>
       </c>
@@ -32793,7 +32835,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11">
       <c r="A346" s="10">
         <v>45508</v>
       </c>
@@ -32828,7 +32870,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11">
       <c r="A347" s="10">
         <v>45515</v>
       </c>
@@ -32863,7 +32905,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11">
       <c r="A348" s="10">
         <v>45522</v>
       </c>
@@ -32898,7 +32940,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11">
       <c r="A349" s="10">
         <v>45529</v>
       </c>
@@ -32933,7 +32975,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11">
       <c r="A350" s="10">
         <v>45536</v>
       </c>
@@ -32968,7 +33010,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11">
       <c r="A351" s="10">
         <v>45543</v>
       </c>
@@ -33003,7 +33045,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11">
       <c r="A352" s="10">
         <v>45550</v>
       </c>
@@ -33038,7 +33080,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11">
       <c r="A353" s="10">
         <v>45557</v>
       </c>
@@ -33073,7 +33115,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11">
       <c r="A354" s="10">
         <v>45564</v>
       </c>
@@ -33108,7 +33150,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11">
       <c r="A355" s="10">
         <v>45571</v>
       </c>
@@ -33143,7 +33185,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11">
       <c r="A356" s="10">
         <v>45578</v>
       </c>
@@ -33178,7 +33220,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11">
       <c r="A357" s="10">
         <v>45585</v>
       </c>
@@ -33213,7 +33255,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11">
       <c r="A358" s="10">
         <v>45592</v>
       </c>
@@ -33248,7 +33290,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11">
       <c r="A359" s="10">
         <v>45599</v>
       </c>
@@ -33283,7 +33325,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11">
       <c r="A360" s="10">
         <v>45606</v>
       </c>
@@ -33318,7 +33360,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11">
       <c r="A361" s="10">
         <v>45613</v>
       </c>
@@ -33353,7 +33395,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11">
       <c r="A362" s="10">
         <v>45620</v>
       </c>
@@ -33388,7 +33430,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11">
       <c r="A363" s="10">
         <v>45627</v>
       </c>
@@ -33423,7 +33465,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11">
       <c r="A364" s="10">
         <v>45634</v>
       </c>
@@ -33458,7 +33500,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11">
       <c r="A365" s="10">
         <v>45641</v>
       </c>
@@ -33493,7 +33535,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11">
       <c r="A366" s="10">
         <v>45648</v>
       </c>
@@ -33528,7 +33570,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11">
       <c r="A367" s="10">
         <v>45655</v>
       </c>
@@ -33563,7 +33605,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11">
       <c r="A368" s="10">
         <v>45662</v>
       </c>
@@ -33598,7 +33640,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11">
       <c r="A369" s="10">
         <v>45669</v>
       </c>
@@ -33633,7 +33675,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11">
       <c r="A370" s="10">
         <v>45676</v>
       </c>
@@ -33668,7 +33710,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11">
       <c r="A371" s="10">
         <v>45683</v>
       </c>
@@ -33703,7 +33745,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11">
       <c r="A372" s="10">
         <v>45690</v>
       </c>
@@ -33738,7 +33780,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11">
       <c r="A373" s="10">
         <v>45697</v>
       </c>
@@ -33773,7 +33815,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11">
       <c r="A374" s="10">
         <v>45704</v>
       </c>
@@ -33808,7 +33850,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11">
       <c r="A375" s="10">
         <v>45711</v>
       </c>
@@ -33843,7 +33885,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11">
       <c r="A376" s="10">
         <v>45718</v>
       </c>
@@ -33878,7 +33920,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11">
       <c r="A377" s="10">
         <v>45725</v>
       </c>
@@ -33913,7 +33955,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11">
       <c r="A378" s="10">
         <v>45732</v>
       </c>
@@ -33948,7 +33990,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11">
       <c r="A379" s="10">
         <v>45739</v>
       </c>
@@ -33983,7 +34025,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11">
       <c r="A380" s="10">
         <v>45746</v>
       </c>
@@ -34018,7 +34060,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11">
       <c r="A381" s="10">
         <v>45753</v>
       </c>
@@ -34053,7 +34095,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11">
       <c r="A382" s="10">
         <v>45760</v>
       </c>
@@ -34088,7 +34130,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11">
       <c r="A383" s="10">
         <v>45767</v>
       </c>
@@ -34123,7 +34165,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11">
       <c r="A384" s="10">
         <v>45774</v>
       </c>
@@ -34158,7 +34200,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11">
       <c r="A385" s="10">
         <v>45781</v>
       </c>
@@ -34193,7 +34235,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11">
       <c r="A386" s="10">
         <v>45788</v>
       </c>
@@ -34228,7 +34270,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11">
       <c r="A387" s="10">
         <v>45795</v>
       </c>
@@ -34263,7 +34305,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11">
       <c r="A388" s="10">
         <v>45802</v>
       </c>
@@ -34298,7 +34340,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11">
       <c r="A389" s="10">
         <v>45809</v>
       </c>
@@ -34333,7 +34375,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11">
       <c r="A390" s="10">
         <v>45816</v>
       </c>
@@ -34368,7 +34410,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11">
       <c r="A391" s="10">
         <v>45823</v>
       </c>
@@ -34403,7 +34445,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11">
       <c r="A392" s="10">
         <v>45830</v>
       </c>
@@ -34438,7 +34480,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11">
       <c r="A393" s="10">
         <v>45837</v>
       </c>
@@ -34473,7 +34515,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11">
       <c r="A394" s="10">
         <v>45844</v>
       </c>
@@ -34508,7 +34550,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11">
       <c r="A395" s="10">
         <v>45851</v>
       </c>
@@ -34543,7 +34585,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11">
       <c r="A396" s="10">
         <v>45858</v>
       </c>
@@ -34578,7 +34620,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11">
       <c r="A397" s="10">
         <v>45865</v>
       </c>
@@ -34613,7 +34655,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11">
       <c r="A398" s="10">
         <v>45872</v>
       </c>
@@ -34648,7 +34690,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11">
       <c r="A399" s="10">
         <v>45879</v>
       </c>
@@ -34683,7 +34725,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11">
       <c r="A400" s="10">
         <v>45886</v>
       </c>
@@ -34718,7 +34760,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11">
       <c r="A401" s="10">
         <v>45893</v>
       </c>
@@ -34753,7 +34795,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11">
       <c r="A402" s="10">
         <v>45900</v>
       </c>
@@ -34788,7 +34830,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11">
       <c r="A403" s="10">
         <v>45907</v>
       </c>
@@ -34823,7 +34865,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11">
       <c r="A404" s="10">
         <v>45914</v>
       </c>
@@ -34858,7 +34900,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11">
       <c r="A405" s="10">
         <v>45921</v>
       </c>
@@ -34893,7 +34935,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11">
       <c r="A406" s="10">
         <v>45928</v>
       </c>
@@ -34928,7 +34970,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11">
       <c r="A407" s="10">
         <v>45935</v>
       </c>
@@ -34963,7 +35005,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11">
       <c r="A408" s="10">
         <v>45942</v>
       </c>
@@ -34998,7 +35040,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11">
       <c r="A409" s="10">
         <v>45949</v>
       </c>
@@ -35033,7 +35075,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11">
       <c r="A410" s="10">
         <v>45956</v>
       </c>
@@ -35068,7 +35110,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11">
       <c r="A411" s="10">
         <v>45963</v>
       </c>
@@ -35103,7 +35145,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11">
       <c r="A412" s="10">
         <v>45970</v>
       </c>
@@ -35138,7 +35180,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11">
       <c r="A413" s="10">
         <v>45977</v>
       </c>
@@ -35173,7 +35215,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11">
       <c r="A414" s="10">
         <v>45984</v>
       </c>
@@ -35208,7 +35250,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11">
       <c r="A415" s="10">
         <v>45991</v>
       </c>
@@ -35243,7 +35285,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11">
       <c r="A416" s="10">
         <v>45998</v>
       </c>
@@ -35278,7 +35320,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11">
       <c r="A417" s="10">
         <v>46005</v>
       </c>
@@ -35313,7 +35355,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11">
       <c r="A418" s="10">
         <v>46012</v>
       </c>
@@ -35348,7 +35390,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11">
       <c r="A419" s="10">
         <v>46026</v>
       </c>
@@ -35383,7 +35425,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11">
       <c r="A420" s="10">
         <v>46033</v>
       </c>
@@ -35418,7 +35460,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11">
       <c r="A421" s="10">
         <v>46040</v>
       </c>
@@ -35453,7 +35495,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11">
       <c r="A422" s="10">
         <v>46047</v>
       </c>
@@ -35488,7 +35530,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11">
       <c r="A423" s="10">
         <v>46054</v>
       </c>
@@ -35523,7 +35565,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11">
       <c r="A424" s="10">
         <v>46061</v>
       </c>
@@ -35558,7 +35600,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11">
       <c r="A425" s="10">
         <v>46068</v>
       </c>
@@ -35593,7 +35635,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11">
       <c r="A426" s="10">
         <v>46075</v>
       </c>
@@ -35628,7 +35670,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11">
       <c r="A427" s="10">
         <v>46082</v>
       </c>
@@ -35663,7 +35705,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11">
       <c r="A428" s="10">
         <v>46089</v>
       </c>
@@ -35698,7 +35740,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11">
       <c r="A429" s="10">
         <v>46096</v>
       </c>
@@ -35733,7 +35775,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11">
       <c r="A430" s="10">
         <v>46103</v>
       </c>
@@ -35768,7 +35810,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11">
       <c r="A431" s="10">
         <v>46110</v>
       </c>
@@ -35803,7 +35845,7 @@
         <v>5348</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11">
       <c r="A432" s="10">
         <v>46117</v>
       </c>
@@ -35838,7 +35880,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11">
       <c r="A433" s="10">
         <v>46124</v>
       </c>
@@ -35873,7 +35915,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11">
       <c r="A434" s="10">
         <v>46131</v>
       </c>
@@ -35908,7 +35950,7 @@
         <v>5837</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11">
       <c r="A435" s="10">
         <v>46138</v>
       </c>
@@ -35943,7 +35985,7 @@
         <v>5881</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11">
       <c r="A436" s="10">
         <v>46145</v>
       </c>
@@ -35978,7 +36020,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11">
       <c r="A437" s="10">
         <v>46152</v>
       </c>
@@ -36013,7 +36055,7 @@
         <v>5909</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11">
       <c r="A438" s="10">
         <v>46159</v>
       </c>
@@ -36048,7 +36090,7 @@
         <v>5807</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11">
       <c r="A439" s="10">
         <v>46166</v>
       </c>
@@ -36083,7 +36125,7 @@
         <v>5932</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11">
       <c r="A440" s="10">
         <v>46173</v>
       </c>
@@ -36118,7 +36160,7 @@
         <v>5984</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11">
       <c r="A441" s="10">
         <v>46180</v>
       </c>
@@ -36153,7 +36195,7 @@
         <v>6121</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11">
       <c r="A442" s="10">
         <v>46187</v>
       </c>
@@ -36188,7 +36230,7 @@
         <v>6025</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11">
       <c r="A443" s="10">
         <v>46194</v>
       </c>
@@ -36223,7 +36265,7 @@
         <v>6239</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11">
       <c r="A444" s="10">
         <v>46201</v>
       </c>
@@ -36258,7 +36300,7 @@
         <v>5992</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11">
       <c r="A445" s="10">
         <v>46208</v>
       </c>
@@ -36293,7 +36335,7 @@
         <v>5634</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11">
       <c r="A446" s="10">
         <v>46215</v>
       </c>
@@ -36328,7 +36370,7 @@
         <v>5533</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11">
       <c r="A447" s="10">
         <v>46222</v>
       </c>
@@ -36363,7 +36405,7 @@
         <v>5473</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11">
       <c r="A448" s="10">
         <v>46229</v>
       </c>
@@ -36398,7 +36440,7 @@
         <v>5463</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11">
       <c r="A449" s="10">
         <v>46236</v>
       </c>
@@ -36433,7 +36475,7 @@
         <v>5322</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11">
       <c r="A450" s="10">
         <v>46243</v>
       </c>
@@ -36468,7 +36510,7 @@
         <v>5409</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11">
       <c r="A451" s="10">
         <v>46250</v>
       </c>
@@ -36501,6 +36543,41 @@
       </c>
       <c r="K451" s="13">
         <v>5383</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11">
+      <c r="A452" s="10">
+        <v>46257</v>
+      </c>
+      <c r="B452" s="11">
+        <v>46258</v>
+      </c>
+      <c r="C452" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D452" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E452" s="13">
+        <v>2419</v>
+      </c>
+      <c r="F452" s="13">
+        <v>1039</v>
+      </c>
+      <c r="G452" s="13">
+        <v>4231</v>
+      </c>
+      <c r="H452" s="13">
+        <v>1056</v>
+      </c>
+      <c r="I452" s="13">
+        <v>1398</v>
+      </c>
+      <c r="J452" s="13">
+        <v>229</v>
+      </c>
+      <c r="K452" s="13">
+        <v>5206</v>
       </c>
     </row>
   </sheetData>
@@ -36514,7 +36591,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
@@ -36530,12 +36607,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" ht="15">
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
@@ -36547,7 +36624,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>

--- a/data_lake/freight/Baltic air freight index.xlsx
+++ b/data_lake/freight/Baltic air freight index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77478159-BD8A-7B49-85DC-89AFD89C351B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADDD914-1C9B-154C-8C95-0C155ED02B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17920" yWindow="780" windowWidth="18080" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1681,6 +1681,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3042,6 +3045,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>2419</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>2423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4438,6 +4444,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5799,6 +5808,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>1039</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>1011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7195,6 +7207,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8556,6 +8571,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>4231</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4211</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9952,6 +9970,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11313,6 +11334,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>1056</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>1179</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12709,6 +12733,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14070,6 +14097,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>1398</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15468,6 +15498,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16829,6 +16862,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>5206</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>5343</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18241,6 +18277,9 @@
                 <c:pt idx="450">
                   <c:v>46258</c:v>
                 </c:pt>
+                <c:pt idx="451">
+                  <c:v>46265</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19602,6 +19641,9 @@
                 </c:pt>
                 <c:pt idx="450">
                   <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20748,7 +20790,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K452"/>
+  <dimension ref="A1:K453"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -36578,6 +36620,41 @@
       </c>
       <c r="K452" s="13">
         <v>5206</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11">
+      <c r="A453" s="10">
+        <v>46264</v>
+      </c>
+      <c r="B453" s="11">
+        <v>46265</v>
+      </c>
+      <c r="C453" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D453" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E453" s="13">
+        <v>2423</v>
+      </c>
+      <c r="F453" s="13">
+        <v>1011</v>
+      </c>
+      <c r="G453" s="13">
+        <v>4211</v>
+      </c>
+      <c r="H453" s="13">
+        <v>1179</v>
+      </c>
+      <c r="I453" s="13">
+        <v>144</v>
+      </c>
+      <c r="J453" s="13">
+        <v>266</v>
+      </c>
+      <c r="K453" s="13">
+        <v>5343</v>
       </c>
     </row>
   </sheetData>
